--- a/dummy_data_raw.xlsx
+++ b/dummy_data_raw.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="375">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="556">
   <si>
     <t>plugin_id</t>
   </si>
@@ -73,472 +73,715 @@
     <t>Low</t>
   </si>
   <si>
-    <t>Production</t>
-  </si>
-  <si>
-    <t>UAT</t>
-  </si>
-  <si>
-    <t>DR</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>Development</t>
-  </si>
-  <si>
-    <t>06/03/2025 19:53:39</t>
-  </si>
-  <si>
-    <t>19/03/2025 20:59:05</t>
-  </si>
-  <si>
-    <t>15/07/2025 11:38:30</t>
-  </si>
-  <si>
-    <t>14/04/2025 08:03:21</t>
-  </si>
-  <si>
-    <t>19/08/2025 07:44:57</t>
-  </si>
-  <si>
-    <t>16/04/2025 22:30:30</t>
-  </si>
-  <si>
-    <t>02/07/2025 05:33:46</t>
-  </si>
-  <si>
-    <t>17/04/2025 02:43:16</t>
-  </si>
-  <si>
-    <t>09/05/2025 19:03:39</t>
-  </si>
-  <si>
-    <t>01/09/2025 16:06:55</t>
-  </si>
-  <si>
-    <t>02/07/2025 09:00:15</t>
-  </si>
-  <si>
-    <t>16/05/2025 03:47:34</t>
-  </si>
-  <si>
-    <t>28/02/2025 10:43:13</t>
-  </si>
-  <si>
-    <t>23/04/2025 20:01:36</t>
-  </si>
-  <si>
-    <t>18/08/2025 17:54:08</t>
-  </si>
-  <si>
-    <t>22/02/2025 19:38:21</t>
-  </si>
-  <si>
-    <t>11/08/2025 12:56:37</t>
-  </si>
-  <si>
-    <t>28/01/2025 12:07:30</t>
-  </si>
-  <si>
-    <t>02/09/2025 14:40:56</t>
-  </si>
-  <si>
-    <t>02/04/2025 20:39:30</t>
-  </si>
-  <si>
-    <t>18/01/2025 02:05:03</t>
-  </si>
-  <si>
-    <t>06/09/2025 22:23:57</t>
-  </si>
-  <si>
-    <t>30/04/2025 23:54:35</t>
-  </si>
-  <si>
-    <t>03/09/2025 17:50:13</t>
-  </si>
-  <si>
-    <t>22/01/2025 11:59:07</t>
-  </si>
-  <si>
-    <t>02/02/2025 15:11:40</t>
-  </si>
-  <si>
-    <t>05/05/2025 11:36:53</t>
-  </si>
-  <si>
-    <t>15/08/2025 03:40:01</t>
-  </si>
-  <si>
-    <t>14/06/2025 03:07:29</t>
-  </si>
-  <si>
-    <t>17/03/2025 05:05:27</t>
-  </si>
-  <si>
-    <t>03/04/2025 21:29:54</t>
-  </si>
-  <si>
-    <t>04/02/2025 17:44:00</t>
-  </si>
-  <si>
-    <t>17/04/2025 10:31:29</t>
-  </si>
-  <si>
-    <t>03/03/2025 02:27:36</t>
-  </si>
-  <si>
-    <t>23/07/2025 22:27:42</t>
-  </si>
-  <si>
-    <t>07/06/2025 14:23:21</t>
-  </si>
-  <si>
-    <t>06/01/2025 06:11:33</t>
-  </si>
-  <si>
-    <t>20/07/2025 23:41:39</t>
-  </si>
-  <si>
-    <t>23/04/2025 11:47:32</t>
-  </si>
-  <si>
-    <t>02/06/2025 23:32:01</t>
-  </si>
-  <si>
-    <t>19/01/2025 05:12:13</t>
-  </si>
-  <si>
-    <t>10/03/2025 05:36:23</t>
-  </si>
-  <si>
-    <t>16/06/2025 11:44:25</t>
-  </si>
-  <si>
-    <t>08/07/2025 07:32:34</t>
-  </si>
-  <si>
-    <t>09/01/2025 00:58:18</t>
-  </si>
-  <si>
-    <t>30/06/2025 03:00:29</t>
-  </si>
-  <si>
-    <t>23/05/2025 03:17:41</t>
-  </si>
-  <si>
-    <t>15/05/2025 02:05:05</t>
-  </si>
-  <si>
-    <t>28/05/2025 12:01:25</t>
-  </si>
-  <si>
-    <t>17/03/2025 08:28:08</t>
-  </si>
-  <si>
-    <t>27/07/2025 05:55:52</t>
-  </si>
-  <si>
-    <t>10/04/2025 21:33:23</t>
-  </si>
-  <si>
-    <t>09/01/2025 01:14:49</t>
-  </si>
-  <si>
-    <t>03/08/2025 01:21:03</t>
-  </si>
-  <si>
-    <t>06/09/2025 19:59:40</t>
-  </si>
-  <si>
-    <t>10/05/2025 06:57:05</t>
-  </si>
-  <si>
-    <t>12/04/2025 20:19:52</t>
-  </si>
-  <si>
-    <t>07/04/2025 20:39:22</t>
-  </si>
-  <si>
-    <t>15/01/2025 19:36:19</t>
-  </si>
-  <si>
-    <t>21/07/2025 06:57:41</t>
-  </si>
-  <si>
-    <t>21/04/2025 13:06:54</t>
-  </si>
-  <si>
-    <t>09/09/2025 02:56:12</t>
-  </si>
-  <si>
-    <t>08/05/2025 06:50:51</t>
-  </si>
-  <si>
-    <t>16/06/2025 19:53:28</t>
-  </si>
-  <si>
-    <t>08/01/2025 23:19:44</t>
-  </si>
-  <si>
-    <t>05/09/2025 02:03:35</t>
-  </si>
-  <si>
-    <t>25/08/2025 05:08:46</t>
-  </si>
-  <si>
-    <t>26/05/2025 17:32:25</t>
-  </si>
-  <si>
-    <t>14/02/2025 18:09:13</t>
-  </si>
-  <si>
-    <t>27/06/2025 02:58:14</t>
-  </si>
-  <si>
-    <t>26/06/2025 01:57:24</t>
-  </si>
-  <si>
-    <t>26/04/2025 21:41:33</t>
-  </si>
-  <si>
-    <t>26/05/2025 08:01:43</t>
-  </si>
-  <si>
-    <t>08/09/2025 20:41:02</t>
-  </si>
-  <si>
-    <t>17/01/2025 16:49:40</t>
-  </si>
-  <si>
-    <t>02/02/2025 05:53:13</t>
-  </si>
-  <si>
-    <t>14/06/2025 12:35:59</t>
-  </si>
-  <si>
-    <t>23/05/2025 17:04:58</t>
-  </si>
-  <si>
-    <t>20/01/2025 01:49:40</t>
-  </si>
-  <si>
-    <t>02/05/2025 01:35:11</t>
-  </si>
-  <si>
-    <t>09/09/2025 15:33:08</t>
-  </si>
-  <si>
-    <t>28/04/2025 07:52:27</t>
-  </si>
-  <si>
-    <t>19/06/2025 15:52:27</t>
-  </si>
-  <si>
-    <t>31/05/2025 16:19:05</t>
-  </si>
-  <si>
-    <t>24/03/2025 03:43:27</t>
-  </si>
-  <si>
-    <t>09/06/2025 03:21:41</t>
-  </si>
-  <si>
-    <t>05/09/2025 05:27:52</t>
-  </si>
-  <si>
-    <t>06/07/2025 10:11:05</t>
-  </si>
-  <si>
-    <t>18/05/2025 06:46:04</t>
-  </si>
-  <si>
-    <t>11/02/2025 13:07:10</t>
-  </si>
-  <si>
-    <t>14/04/2025 17:12:39</t>
-  </si>
-  <si>
-    <t>21/07/2025 16:14:16</t>
-  </si>
-  <si>
-    <t>03/07/2025 05:44:42</t>
-  </si>
-  <si>
-    <t>10/08/2025 11:29:52</t>
-  </si>
-  <si>
-    <t>29/05/2025 23:13:30</t>
-  </si>
-  <si>
-    <t>27/02/2025 04:03:45</t>
-  </si>
-  <si>
-    <t>29/03/2025 14:47:24</t>
-  </si>
-  <si>
-    <t>02/03/2025 19:13:10</t>
-  </si>
-  <si>
-    <t>01/04/2025 04:57:41</t>
-  </si>
-  <si>
-    <t>25/01/2025 12:52:46</t>
-  </si>
-  <si>
-    <t>17/06/2025 15:46:52</t>
-  </si>
-  <si>
-    <t>13/02/2025 14:18:03</t>
-  </si>
-  <si>
-    <t>22/06/2025 01:48:42</t>
-  </si>
-  <si>
-    <t>28/02/2025 05:52:09</t>
-  </si>
-  <si>
-    <t>30/07/2025 13:27:24</t>
-  </si>
-  <si>
-    <t>19/06/2025 03:52:49</t>
-  </si>
-  <si>
-    <t>31/07/2025 22:59:15</t>
-  </si>
-  <si>
-    <t>09/09/2025 20:15:36</t>
-  </si>
-  <si>
-    <t>11/03/2025 18:32:12</t>
-  </si>
-  <si>
-    <t>18/02/2025 21:29:25</t>
-  </si>
-  <si>
-    <t>04/02/2025 08:08:39</t>
-  </si>
-  <si>
-    <t>11/03/2025 20:24:57</t>
-  </si>
-  <si>
-    <t>02/07/2025 16:07:02</t>
-  </si>
-  <si>
-    <t>11/04/2025 01:56:19</t>
-  </si>
-  <si>
-    <t>24/02/2025 00:57:07</t>
-  </si>
-  <si>
-    <t>30/03/2025 15:20:17</t>
-  </si>
-  <si>
-    <t>09/02/2025 23:16:11</t>
-  </si>
-  <si>
-    <t>22/04/2025 13:00:27</t>
-  </si>
-  <si>
-    <t>15/05/2025 20:59:04</t>
-  </si>
-  <si>
-    <t>13/02/2025 21:22:15</t>
-  </si>
-  <si>
-    <t>25/01/2025 13:15:16</t>
-  </si>
-  <si>
-    <t>01/03/2025 15:45:53</t>
-  </si>
-  <si>
-    <t>30/01/2025 21:52:19</t>
-  </si>
-  <si>
-    <t>18/05/2025 02:17:27</t>
-  </si>
-  <si>
-    <t>24/08/2025 05:49:39</t>
-  </si>
-  <si>
-    <t>05/05/2025 14:42:07</t>
-  </si>
-  <si>
-    <t>19/03/2025 14:45:47</t>
-  </si>
-  <si>
-    <t>02/06/2025 23:02:55</t>
-  </si>
-  <si>
-    <t>30/08/2025 08:02:46</t>
-  </si>
-  <si>
-    <t>16/06/2025 00:38:37</t>
-  </si>
-  <si>
-    <t>12/07/2025 10:11:05</t>
-  </si>
-  <si>
-    <t>23/05/2025 18:39:36</t>
-  </si>
-  <si>
-    <t>15/02/2025 23:24:28</t>
-  </si>
-  <si>
-    <t>17/02/2025 02:14:25</t>
-  </si>
-  <si>
-    <t>07/05/2025 02:16:37</t>
-  </si>
-  <si>
-    <t>27/03/2025 22:57:41</t>
-  </si>
-  <si>
-    <t>17/02/2025 23:48:40</t>
-  </si>
-  <si>
-    <t>08/03/2025 21:29:31</t>
-  </si>
-  <si>
-    <t>21/03/2025 15:36:58</t>
-  </si>
-  <si>
-    <t>09/09/2025 01:20:02</t>
-  </si>
-  <si>
-    <t>30/03/2025 23:32:59</t>
-  </si>
-  <si>
-    <t>01/07/2025 08:02:19</t>
-  </si>
-  <si>
-    <t>18/05/2025 21:31:06</t>
-  </si>
-  <si>
-    <t>17/01/2025 10:47:59</t>
-  </si>
-  <si>
-    <t>11/02/2025 23:29:01</t>
-  </si>
-  <si>
-    <t>18/01/2025 05:46:53</t>
-  </si>
-  <si>
-    <t>25/07/2025 17:52:30</t>
-  </si>
-  <si>
-    <t>31/08/2025 17:43:23</t>
-  </si>
-  <si>
-    <t>14/06/2025 21:02:38</t>
-  </si>
-  <si>
-    <t>22/02/2025 03:08:18</t>
-  </si>
-  <si>
-    <t>11/08/2025 22:06:34</t>
+    <t>DR-DB</t>
+  </si>
+  <si>
+    <t>DR-App</t>
+  </si>
+  <si>
+    <t>UAT-Web</t>
+  </si>
+  <si>
+    <t>Prod-Web</t>
+  </si>
+  <si>
+    <t>Dev-App</t>
+  </si>
+  <si>
+    <t>Dev-Web</t>
+  </si>
+  <si>
+    <t>Prod-App</t>
+  </si>
+  <si>
+    <t>UAT-App</t>
+  </si>
+  <si>
+    <t>DR-Web</t>
+  </si>
+  <si>
+    <t>UAT-DB</t>
+  </si>
+  <si>
+    <t>Dev-DB</t>
+  </si>
+  <si>
+    <t>Prod-DB</t>
+  </si>
+  <si>
+    <t>17/10/2025 21:31:51</t>
+  </si>
+  <si>
+    <t>21/12/2025 22:52:34</t>
+  </si>
+  <si>
+    <t>16/01/2026 01:44:31</t>
+  </si>
+  <si>
+    <t>10/12/2025 16:04:20</t>
+  </si>
+  <si>
+    <t>28/12/2025 16:26:19</t>
+  </si>
+  <si>
+    <t>18/12/2025 17:01:11</t>
+  </si>
+  <si>
+    <t>21/01/2026 17:56:46</t>
+  </si>
+  <si>
+    <t>03/11/2025 10:44:59</t>
+  </si>
+  <si>
+    <t>13/12/2025 11:08:30</t>
+  </si>
+  <si>
+    <t>16/01/2026 06:57:56</t>
+  </si>
+  <si>
+    <t>13/10/2025 00:17:50</t>
+  </si>
+  <si>
+    <t>11/10/2025 21:21:50</t>
+  </si>
+  <si>
+    <t>08/10/2025 11:36:19</t>
+  </si>
+  <si>
+    <t>03/02/2026 22:41:47</t>
+  </si>
+  <si>
+    <t>08/01/2026 03:54:07</t>
+  </si>
+  <si>
+    <t>01/01/2026 06:27:07</t>
+  </si>
+  <si>
+    <t>13/11/2025 04:24:56</t>
+  </si>
+  <si>
+    <t>21/12/2025 19:05:42</t>
+  </si>
+  <si>
+    <t>22/10/2025 06:13:37</t>
+  </si>
+  <si>
+    <t>21/11/2025 00:17:54</t>
+  </si>
+  <si>
+    <t>06/11/2025 11:58:38</t>
+  </si>
+  <si>
+    <t>21/10/2025 13:23:01</t>
+  </si>
+  <si>
+    <t>12/01/2026 05:47:39</t>
+  </si>
+  <si>
+    <t>28/01/2026 00:35:01</t>
+  </si>
+  <si>
+    <t>19/01/2026 15:16:18</t>
+  </si>
+  <si>
+    <t>18/12/2025 11:38:39</t>
+  </si>
+  <si>
+    <t>26/09/2025 17:50:56</t>
+  </si>
+  <si>
+    <t>17/10/2025 08:12:40</t>
+  </si>
+  <si>
+    <t>18/10/2025 12:13:21</t>
+  </si>
+  <si>
+    <t>13/10/2025 17:23:19</t>
+  </si>
+  <si>
+    <t>15/02/2026 02:59:42</t>
+  </si>
+  <si>
+    <t>23/10/2025 01:44:25</t>
+  </si>
+  <si>
+    <t>18/01/2026 13:20:05</t>
+  </si>
+  <si>
+    <t>04/02/2026 19:24:40</t>
+  </si>
+  <si>
+    <t>17/02/2026 18:56:55</t>
+  </si>
+  <si>
+    <t>14/11/2025 14:06:55</t>
+  </si>
+  <si>
+    <t>21/01/2026 08:30:10</t>
+  </si>
+  <si>
+    <t>28/11/2025 00:05:28</t>
+  </si>
+  <si>
+    <t>12/02/2026 10:56:30</t>
+  </si>
+  <si>
+    <t>20/02/2026 13:33:51</t>
+  </si>
+  <si>
+    <t>04/10/2025 12:29:20</t>
+  </si>
+  <si>
+    <t>03/01/2026 23:16:49</t>
+  </si>
+  <si>
+    <t>17/12/2025 21:32:51</t>
+  </si>
+  <si>
+    <t>29/09/2025 07:55:59</t>
+  </si>
+  <si>
+    <t>06/10/2025 14:05:48</t>
+  </si>
+  <si>
+    <t>21/11/2025 08:23:36</t>
+  </si>
+  <si>
+    <t>18/10/2025 13:27:44</t>
+  </si>
+  <si>
+    <t>23/01/2026 22:16:42</t>
+  </si>
+  <si>
+    <t>24/01/2026 13:13:36</t>
+  </si>
+  <si>
+    <t>06/12/2025 00:13:37</t>
+  </si>
+  <si>
+    <t>02/10/2025 23:22:37</t>
+  </si>
+  <si>
+    <t>22/02/2026 12:53:33</t>
+  </si>
+  <si>
+    <t>13/11/2025 00:59:02</t>
+  </si>
+  <si>
+    <t>06/11/2025 08:07:53</t>
+  </si>
+  <si>
+    <t>24/09/2025 20:49:08</t>
+  </si>
+  <si>
+    <t>03/10/2025 19:52:40</t>
+  </si>
+  <si>
+    <t>02/02/2026 23:49:56</t>
+  </si>
+  <si>
+    <t>04/01/2026 17:03:52</t>
+  </si>
+  <si>
+    <t>07/10/2025 17:15:02</t>
+  </si>
+  <si>
+    <t>19/01/2026 13:54:42</t>
+  </si>
+  <si>
+    <t>01/10/2025 06:43:02</t>
+  </si>
+  <si>
+    <t>27/11/2025 18:10:02</t>
+  </si>
+  <si>
+    <t>26/11/2025 01:05:59</t>
+  </si>
+  <si>
+    <t>13/11/2025 16:56:58</t>
+  </si>
+  <si>
+    <t>26/09/2025 16:05:29</t>
+  </si>
+  <si>
+    <t>27/10/2025 12:14:27</t>
+  </si>
+  <si>
+    <t>04/01/2026 13:22:24</t>
+  </si>
+  <si>
+    <t>09/10/2025 17:03:02</t>
+  </si>
+  <si>
+    <t>29/12/2025 16:37:57</t>
+  </si>
+  <si>
+    <t>17/10/2025 18:00:03</t>
+  </si>
+  <si>
+    <t>29/12/2025 11:46:57</t>
+  </si>
+  <si>
+    <t>13/02/2026 10:16:59</t>
+  </si>
+  <si>
+    <t>12/12/2025 18:39:22</t>
+  </si>
+  <si>
+    <t>18/01/2026 09:00:07</t>
+  </si>
+  <si>
+    <t>27/01/2026 04:06:47</t>
+  </si>
+  <si>
+    <t>23/01/2026 04:41:34</t>
+  </si>
+  <si>
+    <t>06/10/2025 15:59:14</t>
+  </si>
+  <si>
+    <t>04/11/2025 22:07:57</t>
+  </si>
+  <si>
+    <t>10/02/2026 16:57:57</t>
+  </si>
+  <si>
+    <t>17/01/2026 14:06:48</t>
+  </si>
+  <si>
+    <t>19/10/2025 00:57:21</t>
+  </si>
+  <si>
+    <t>06/02/2026 06:17:39</t>
+  </si>
+  <si>
+    <t>01/02/2026 06:06:21</t>
+  </si>
+  <si>
+    <t>14/10/2025 23:52:48</t>
+  </si>
+  <si>
+    <t>17/01/2026 14:28:24</t>
+  </si>
+  <si>
+    <t>23/11/2025 08:48:04</t>
+  </si>
+  <si>
+    <t>12/11/2025 22:19:09</t>
+  </si>
+  <si>
+    <t>29/12/2025 21:16:08</t>
+  </si>
+  <si>
+    <t>05/12/2025 23:49:57</t>
+  </si>
+  <si>
+    <t>30/10/2025 16:47:27</t>
+  </si>
+  <si>
+    <t>02/01/2026 00:15:01</t>
+  </si>
+  <si>
+    <t>28/12/2025 22:52:55</t>
+  </si>
+  <si>
+    <t>09/10/2025 16:24:36</t>
+  </si>
+  <si>
+    <t>27/01/2026 16:16:16</t>
+  </si>
+  <si>
+    <t>10/12/2025 07:47:51</t>
+  </si>
+  <si>
+    <t>16/10/2025 23:37:45</t>
+  </si>
+  <si>
+    <t>10/11/2025 22:28:56</t>
+  </si>
+  <si>
+    <t>25/01/2026 15:29:51</t>
+  </si>
+  <si>
+    <t>06/11/2025 01:00:58</t>
+  </si>
+  <si>
+    <t>26/11/2025 11:06:53</t>
+  </si>
+  <si>
+    <t>11/12/2025 20:24:18</t>
+  </si>
+  <si>
+    <t>15/10/2025 23:20:56</t>
+  </si>
+  <si>
+    <t>08/11/2025 00:49:22</t>
+  </si>
+  <si>
+    <t>03/10/2025 12:32:30</t>
+  </si>
+  <si>
+    <t>19/01/2026 08:51:30</t>
+  </si>
+  <si>
+    <t>13/12/2025 17:16:10</t>
+  </si>
+  <si>
+    <t>25/10/2025 10:18:03</t>
+  </si>
+  <si>
+    <t>25/01/2026 09:23:44</t>
+  </si>
+  <si>
+    <t>01/11/2025 04:07:52</t>
+  </si>
+  <si>
+    <t>09/01/2026 15:28:19</t>
+  </si>
+  <si>
+    <t>21/01/2026 15:45:56</t>
+  </si>
+  <si>
+    <t>22/01/2026 09:21:50</t>
+  </si>
+  <si>
+    <t>15/01/2026 08:38:58</t>
+  </si>
+  <si>
+    <t>26/12/2025 06:13:33</t>
+  </si>
+  <si>
+    <t>19/11/2025 16:24:45</t>
+  </si>
+  <si>
+    <t>04/10/2025 19:39:51</t>
+  </si>
+  <si>
+    <t>02/12/2025 09:04:37</t>
+  </si>
+  <si>
+    <t>18/02/2026 08:56:14</t>
+  </si>
+  <si>
+    <t>15/10/2025 23:27:56</t>
+  </si>
+  <si>
+    <t>12/11/2025 05:59:51</t>
+  </si>
+  <si>
+    <t>31/10/2025 23:09:26</t>
+  </si>
+  <si>
+    <t>20/12/2025 07:11:19</t>
+  </si>
+  <si>
+    <t>21/10/2025 23:55:00</t>
+  </si>
+  <si>
+    <t>17/11/2025 02:42:07</t>
+  </si>
+  <si>
+    <t>05/02/2026 16:18:27</t>
+  </si>
+  <si>
+    <t>25/12/2025 05:38:46</t>
+  </si>
+  <si>
+    <t>29/10/2025 14:53:07</t>
+  </si>
+  <si>
+    <t>06/11/2025 05:07:05</t>
+  </si>
+  <si>
+    <t>14/10/2025 17:21:41</t>
+  </si>
+  <si>
+    <t>17/01/2026 17:02:10</t>
+  </si>
+  <si>
+    <t>16/01/2026 05:31:43</t>
+  </si>
+  <si>
+    <t>30/01/2026 00:27:37</t>
+  </si>
+  <si>
+    <t>24/12/2025 10:31:16</t>
+  </si>
+  <si>
+    <t>08/12/2025 18:27:21</t>
+  </si>
+  <si>
+    <t>07/10/2025 03:44:49</t>
+  </si>
+  <si>
+    <t>09/02/2026 12:04:13</t>
+  </si>
+  <si>
+    <t>08/01/2026 12:40:09</t>
+  </si>
+  <si>
+    <t>27/09/2025 17:46:56</t>
+  </si>
+  <si>
+    <t>07/12/2025 20:56:09</t>
+  </si>
+  <si>
+    <t>05/12/2025 11:40:11</t>
+  </si>
+  <si>
+    <t>08/12/2025 14:43:16</t>
+  </si>
+  <si>
+    <t>05/10/2025 16:02:29</t>
+  </si>
+  <si>
+    <t>26/12/2025 02:36:14</t>
+  </si>
+  <si>
+    <t>09/12/2025 23:59:18</t>
+  </si>
+  <si>
+    <t>17/12/2025 06:02:23</t>
+  </si>
+  <si>
+    <t>27/11/2025 11:45:04</t>
+  </si>
+  <si>
+    <t>25/10/2025 07:18:56</t>
+  </si>
+  <si>
+    <t>07/01/2026 03:20:16</t>
+  </si>
+  <si>
+    <t>23/02/2026 23:33:07</t>
+  </si>
+  <si>
+    <t>14/12/2025 01:14:37</t>
+  </si>
+  <si>
+    <t>09/12/2025 00:56:34</t>
+  </si>
+  <si>
+    <t>04/12/2025 03:47:22</t>
+  </si>
+  <si>
+    <t>20/10/2025 03:11:52</t>
+  </si>
+  <si>
+    <t>03/12/2025 01:35:10</t>
+  </si>
+  <si>
+    <t>16/11/2025 11:36:35</t>
+  </si>
+  <si>
+    <t>25/10/2025 05:58:27</t>
+  </si>
+  <si>
+    <t>25/12/2025 02:55:39</t>
+  </si>
+  <si>
+    <t>30/12/2025 23:49:47</t>
+  </si>
+  <si>
+    <t>09/12/2025 09:33:46</t>
+  </si>
+  <si>
+    <t>25/10/2025 08:56:10</t>
+  </si>
+  <si>
+    <t>24/12/2025 00:52:53</t>
+  </si>
+  <si>
+    <t>27/11/2025 18:44:17</t>
+  </si>
+  <si>
+    <t>23/02/2026 10:35:57</t>
+  </si>
+  <si>
+    <t>17/01/2026 12:36:49</t>
+  </si>
+  <si>
+    <t>17/02/2026 21:42:08</t>
+  </si>
+  <si>
+    <t>09/01/2026 06:33:18</t>
+  </si>
+  <si>
+    <t>09/02/2026 08:03:42</t>
+  </si>
+  <si>
+    <t>28/11/2025 07:49:21</t>
+  </si>
+  <si>
+    <t>15/01/2026 10:32:40</t>
+  </si>
+  <si>
+    <t>06/12/2025 06:23:51</t>
+  </si>
+  <si>
+    <t>27/11/2025 17:12:46</t>
+  </si>
+  <si>
+    <t>25/10/2025 20:21:15</t>
+  </si>
+  <si>
+    <t>21/10/2025 18:13:33</t>
+  </si>
+  <si>
+    <t>01/01/2026 08:41:09</t>
+  </si>
+  <si>
+    <t>24/01/2026 03:45:25</t>
+  </si>
+  <si>
+    <t>16/01/2026 08:08:03</t>
+  </si>
+  <si>
+    <t>02/01/2026 03:19:24</t>
+  </si>
+  <si>
+    <t>29/09/2025 23:31:10</t>
+  </si>
+  <si>
+    <t>27/01/2026 01:19:55</t>
+  </si>
+  <si>
+    <t>28/11/2025 01:24:14</t>
+  </si>
+  <si>
+    <t>27/12/2025 21:08:05</t>
+  </si>
+  <si>
+    <t>12/01/2026 13:23:17</t>
+  </si>
+  <si>
+    <t>18/01/2026 07:02:19</t>
+  </si>
+  <si>
+    <t>11/11/2025 00:09:58</t>
+  </si>
+  <si>
+    <t>28/01/2026 13:08:13</t>
+  </si>
+  <si>
+    <t>09/12/2025 03:14:19</t>
+  </si>
+  <si>
+    <t>08/11/2025 16:55:21</t>
+  </si>
+  <si>
+    <t>22/11/2025 00:14:06</t>
+  </si>
+  <si>
+    <t>01/02/2026 09:44:16</t>
+  </si>
+  <si>
+    <t>02/11/2025 20:38:00</t>
+  </si>
+  <si>
+    <t>09/12/2025 00:40:02</t>
+  </si>
+  <si>
+    <t>04/02/2026 14:03:10</t>
+  </si>
+  <si>
+    <t>22/02/2026 16:11:32</t>
+  </si>
+  <si>
+    <t>22/01/2026 12:49:34</t>
+  </si>
+  <si>
+    <t>05/11/2025 14:58:30</t>
+  </si>
+  <si>
+    <t>14/01/2026 01:10:26</t>
+  </si>
+  <si>
+    <t>14/01/2026 09:17:41</t>
+  </si>
+  <si>
+    <t>04/10/2025 20:40:13</t>
+  </si>
+  <si>
+    <t>31/10/2025 22:36:55</t>
+  </si>
+  <si>
+    <t>03/12/2025 18:38:31</t>
+  </si>
+  <si>
+    <t>21/01/2026 15:00:52</t>
+  </si>
+  <si>
+    <t>07/02/2026 04:06:28</t>
+  </si>
+  <si>
+    <t>19/10/2025 02:41:07</t>
+  </si>
+  <si>
+    <t>03/12/2025 03:45:53</t>
+  </si>
+  <si>
+    <t>21/10/2025 11:14:08</t>
+  </si>
+  <si>
+    <t>15/01/2026 19:17:36</t>
+  </si>
+  <si>
+    <t>18/10/2025 21:36:34</t>
+  </si>
+  <si>
+    <t>20/11/2025 20:51:26</t>
+  </si>
+  <si>
+    <t>27/11/2025 10:38:00</t>
+  </si>
+  <si>
+    <t>22/10/2025 17:52:41</t>
+  </si>
+  <si>
+    <t>26/10/2025 08:21:02</t>
+  </si>
+  <si>
+    <t>11/11/2025 06:29:20</t>
+  </si>
+  <si>
+    <t>12/11/2025 02:37:57</t>
+  </si>
+  <si>
+    <t>02/11/2025 14:50:03</t>
+  </si>
+  <si>
+    <t>11/10/2025 08:50:16</t>
+  </si>
+  <si>
+    <t>07/11/2025 08:18:41</t>
+  </si>
+  <si>
+    <t>07/10/2025 21:46:46</t>
+  </si>
+  <si>
+    <t>15/12/2025 18:28:29</t>
+  </si>
+  <si>
+    <t>27/12/2025 06:23:53</t>
+  </si>
+  <si>
+    <t>06/01/2026 09:00:32</t>
+  </si>
+  <si>
+    <t>10/11/2025 15:43:20</t>
+  </si>
+  <si>
+    <t>12/12/2025 04:52:17</t>
+  </si>
+  <si>
+    <t>07/10/2025 10:33:22</t>
+  </si>
+  <si>
+    <t>19/02/2026 16:22:03</t>
+  </si>
+  <si>
+    <t>26/12/2025 09:21:25</t>
   </si>
   <si>
     <t>18/01/2025 16:07:14</t>
@@ -1139,6 +1382,306 @@
   </si>
   <si>
     <t>16/01/2025 22:19:36</t>
+  </si>
+  <si>
+    <t>03/09/2025 18:27:54</t>
+  </si>
+  <si>
+    <t>15/04/2025 07:10:38</t>
+  </si>
+  <si>
+    <t>14/06/2025 19:38:25</t>
+  </si>
+  <si>
+    <t>28/08/2025 14:07:31</t>
+  </si>
+  <si>
+    <t>13/03/2025 17:11:51</t>
+  </si>
+  <si>
+    <t>22/05/2025 13:29:17</t>
+  </si>
+  <si>
+    <t>01/03/2025 17:39:57</t>
+  </si>
+  <si>
+    <t>04/06/2025 22:48:19</t>
+  </si>
+  <si>
+    <t>07/04/2025 23:56:02</t>
+  </si>
+  <si>
+    <t>26/04/2025 00:35:05</t>
+  </si>
+  <si>
+    <t>12/04/2025 22:04:46</t>
+  </si>
+  <si>
+    <t>29/08/2025 00:44:22</t>
+  </si>
+  <si>
+    <t>15/05/2025 02:46:55</t>
+  </si>
+  <si>
+    <t>13/04/2025 05:11:33</t>
+  </si>
+  <si>
+    <t>20/03/2025 15:03:22</t>
+  </si>
+  <si>
+    <t>11/01/2025 06:21:23</t>
+  </si>
+  <si>
+    <t>16/03/2025 00:02:56</t>
+  </si>
+  <si>
+    <t>18/01/2025 02:14:06</t>
+  </si>
+  <si>
+    <t>28/04/2025 18:24:34</t>
+  </si>
+  <si>
+    <t>09/04/2025 14:43:10</t>
+  </si>
+  <si>
+    <t>28/01/2025 02:23:09</t>
+  </si>
+  <si>
+    <t>25/05/2025 07:32:22</t>
+  </si>
+  <si>
+    <t>23/07/2025 08:04:43</t>
+  </si>
+  <si>
+    <t>04/01/2025 02:51:36</t>
+  </si>
+  <si>
+    <t>13/01/2025 14:10:17</t>
+  </si>
+  <si>
+    <t>02/03/2025 12:46:23</t>
+  </si>
+  <si>
+    <t>15/03/2025 17:29:04</t>
+  </si>
+  <si>
+    <t>15/08/2025 07:45:20</t>
+  </si>
+  <si>
+    <t>07/03/2025 04:57:48</t>
+  </si>
+  <si>
+    <t>01/06/2025 13:16:45</t>
+  </si>
+  <si>
+    <t>15/01/2025 04:09:19</t>
+  </si>
+  <si>
+    <t>28/04/2025 10:47:56</t>
+  </si>
+  <si>
+    <t>09/07/2025 10:34:33</t>
+  </si>
+  <si>
+    <t>09/04/2025 16:09:02</t>
+  </si>
+  <si>
+    <t>13/08/2025 15:06:16</t>
+  </si>
+  <si>
+    <t>08/06/2025 08:16:00</t>
+  </si>
+  <si>
+    <t>07/09/2025 18:15:19</t>
+  </si>
+  <si>
+    <t>28/04/2025 20:28:54</t>
+  </si>
+  <si>
+    <t>08/05/2025 04:58:43</t>
+  </si>
+  <si>
+    <t>05/07/2025 05:57:34</t>
+  </si>
+  <si>
+    <t>25/05/2025 16:13:29</t>
+  </si>
+  <si>
+    <t>31/08/2025 23:43:36</t>
+  </si>
+  <si>
+    <t>11/08/2025 11:44:16</t>
+  </si>
+  <si>
+    <t>11/01/2025 07:08:38</t>
+  </si>
+  <si>
+    <t>05/02/2025 12:55:15</t>
+  </si>
+  <si>
+    <t>18/08/2025 12:15:37</t>
+  </si>
+  <si>
+    <t>06/06/2025 19:29:32</t>
+  </si>
+  <si>
+    <t>17/08/2025 16:07:00</t>
+  </si>
+  <si>
+    <t>23/08/2025 13:09:47</t>
+  </si>
+  <si>
+    <t>22/03/2025 17:28:37</t>
+  </si>
+  <si>
+    <t>11/04/2025 01:04:16</t>
+  </si>
+  <si>
+    <t>18/03/2025 12:51:43</t>
+  </si>
+  <si>
+    <t>09/05/2025 15:27:42</t>
+  </si>
+  <si>
+    <t>28/02/2025 11:42:41</t>
+  </si>
+  <si>
+    <t>24/05/2025 22:12:29</t>
+  </si>
+  <si>
+    <t>19/05/2025 15:55:52</t>
+  </si>
+  <si>
+    <t>24/04/2025 17:15:50</t>
+  </si>
+  <si>
+    <t>21/04/2025 17:53:55</t>
+  </si>
+  <si>
+    <t>23/05/2025 12:22:42</t>
+  </si>
+  <si>
+    <t>16/03/2025 02:36:10</t>
+  </si>
+  <si>
+    <t>22/07/2025 09:51:20</t>
+  </si>
+  <si>
+    <t>24/02/2025 09:10:17</t>
+  </si>
+  <si>
+    <t>20/06/2025 02:37:22</t>
+  </si>
+  <si>
+    <t>18/08/2025 08:26:26</t>
+  </si>
+  <si>
+    <t>24/04/2025 18:07:36</t>
+  </si>
+  <si>
+    <t>05/09/2025 17:54:07</t>
+  </si>
+  <si>
+    <t>06/01/2025 17:39:50</t>
+  </si>
+  <si>
+    <t>30/01/2025 03:40:25</t>
+  </si>
+  <si>
+    <t>20/04/2025 19:34:15</t>
+  </si>
+  <si>
+    <t>13/03/2025 05:13:12</t>
+  </si>
+  <si>
+    <t>17/05/2025 09:25:33</t>
+  </si>
+  <si>
+    <t>09/06/2025 12:08:57</t>
+  </si>
+  <si>
+    <t>28/01/2025 11:17:40</t>
+  </si>
+  <si>
+    <t>25/07/2025 17:15:22</t>
+  </si>
+  <si>
+    <t>04/02/2025 07:55:01</t>
+  </si>
+  <si>
+    <t>16/06/2025 19:09:33</t>
+  </si>
+  <si>
+    <t>02/02/2025 15:44:33</t>
+  </si>
+  <si>
+    <t>10/08/2025 03:26:23</t>
+  </si>
+  <si>
+    <t>15/04/2025 16:48:14</t>
+  </si>
+  <si>
+    <t>04/02/2025 06:25:50</t>
+  </si>
+  <si>
+    <t>09/06/2025 03:01:09</t>
+  </si>
+  <si>
+    <t>12/03/2025 03:01:24</t>
+  </si>
+  <si>
+    <t>23/02/2025 15:24:18</t>
+  </si>
+  <si>
+    <t>15/02/2025 15:34:33</t>
+  </si>
+  <si>
+    <t>09/09/2025 12:57:02</t>
+  </si>
+  <si>
+    <t>16/02/2025 22:13:56</t>
+  </si>
+  <si>
+    <t>29/05/2025 16:14:09</t>
+  </si>
+  <si>
+    <t>02/07/2025 02:31:30</t>
+  </si>
+  <si>
+    <t>23/08/2025 22:38:07</t>
+  </si>
+  <si>
+    <t>20/01/2025 18:43:14</t>
+  </si>
+  <si>
+    <t>28/07/2025 14:21:20</t>
+  </si>
+  <si>
+    <t>04/09/2025 22:32:50</t>
+  </si>
+  <si>
+    <t>11/05/2025 15:59:56</t>
+  </si>
+  <si>
+    <t>04/05/2025 11:29:44</t>
+  </si>
+  <si>
+    <t>18/03/2025 10:22:23</t>
+  </si>
+  <si>
+    <t>22/03/2025 20:29:14</t>
+  </si>
+  <si>
+    <t>26/07/2025 13:51:59</t>
+  </si>
+  <si>
+    <t>26/01/2025 10:46:04</t>
+  </si>
+  <si>
+    <t>22/02/2025 16:14:47</t>
+  </si>
+  <si>
+    <t>04/07/2025 01:35:08</t>
   </si>
 </sst>
 </file>
@@ -1496,7 +2039,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G201"/>
+  <dimension ref="A1:G301"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -1539,10 +2082,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>175</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1562,10 +2105,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>176</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1579,16 +2122,16 @@
         <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G4" t="s">
-        <v>177</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1602,16 +2145,16 @@
         <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>178</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1625,16 +2168,16 @@
         <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G6" t="s">
-        <v>179</v>
+        <v>260</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1648,16 +2191,16 @@
         <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>180</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1671,16 +2214,16 @@
         <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G8" t="s">
-        <v>181</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1694,16 +2237,16 @@
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G9" t="s">
-        <v>182</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1717,16 +2260,16 @@
         <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E10">
         <v>22</v>
       </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G10" t="s">
-        <v>183</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1740,13 +2283,13 @@
         <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="G11" t="s">
-        <v>184</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1760,16 +2303,16 @@
         <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E12">
         <v>443</v>
       </c>
       <c r="F12" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G12" t="s">
-        <v>185</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1783,13 +2326,13 @@
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E13">
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>186</v>
+        <v>267</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1803,16 +2346,16 @@
         <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E14">
         <v>22</v>
       </c>
       <c r="F14" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G14" t="s">
-        <v>187</v>
+        <v>268</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1826,16 +2369,16 @@
         <v>16</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G15" t="s">
-        <v>188</v>
+        <v>269</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1849,13 +2392,13 @@
         <v>17</v>
       </c>
       <c r="D16" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E16">
         <v>0</v>
       </c>
       <c r="G16" t="s">
-        <v>189</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1869,16 +2412,16 @@
         <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E17">
         <v>80</v>
       </c>
       <c r="F17" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G17" t="s">
-        <v>190</v>
+        <v>271</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1892,16 +2435,16 @@
         <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E18">
         <v>443</v>
       </c>
       <c r="F18" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="G18" t="s">
-        <v>191</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1915,16 +2458,16 @@
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E19">
         <v>80</v>
       </c>
       <c r="F19" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G19" t="s">
-        <v>192</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1938,16 +2481,16 @@
         <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="G20" t="s">
-        <v>193</v>
+        <v>274</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1961,16 +2504,16 @@
         <v>17</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G21" t="s">
-        <v>194</v>
+        <v>275</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1984,16 +2527,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E22">
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G22" t="s">
-        <v>195</v>
+        <v>276</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2007,13 +2550,13 @@
         <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E23">
         <v>22</v>
       </c>
       <c r="G23" t="s">
-        <v>196</v>
+        <v>277</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2027,16 +2570,16 @@
         <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E24">
         <v>443</v>
       </c>
       <c r="F24" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G24" t="s">
-        <v>197</v>
+        <v>278</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2050,13 +2593,13 @@
         <v>16</v>
       </c>
       <c r="D25" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E25">
         <v>22</v>
       </c>
       <c r="G25" t="s">
-        <v>198</v>
+        <v>279</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2070,16 +2613,16 @@
         <v>17</v>
       </c>
       <c r="D26" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
       <c r="F26" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G26" t="s">
-        <v>199</v>
+        <v>280</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2093,16 +2636,16 @@
         <v>17</v>
       </c>
       <c r="D27" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E27">
         <v>22</v>
       </c>
       <c r="F27" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G27" t="s">
-        <v>200</v>
+        <v>281</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2116,16 +2659,16 @@
         <v>15</v>
       </c>
       <c r="D28" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G28" t="s">
-        <v>201</v>
+        <v>282</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2139,16 +2682,16 @@
         <v>17</v>
       </c>
       <c r="D29" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G29" t="s">
-        <v>202</v>
+        <v>283</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2162,13 +2705,13 @@
         <v>15</v>
       </c>
       <c r="D30" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E30">
         <v>22</v>
       </c>
       <c r="G30" t="s">
-        <v>203</v>
+        <v>284</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2188,10 +2731,10 @@
         <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G31" t="s">
-        <v>204</v>
+        <v>285</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2205,16 +2748,16 @@
         <v>17</v>
       </c>
       <c r="D32" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E32">
         <v>0</v>
       </c>
       <c r="F32" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="G32" t="s">
-        <v>205</v>
+        <v>286</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2228,13 +2771,13 @@
         <v>17</v>
       </c>
       <c r="D33" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E33">
         <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>206</v>
+        <v>287</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2254,10 +2797,10 @@
         <v>0</v>
       </c>
       <c r="F34" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G34" t="s">
-        <v>207</v>
+        <v>288</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2271,13 +2814,13 @@
         <v>15</v>
       </c>
       <c r="D35" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E35">
         <v>0</v>
       </c>
       <c r="G35" t="s">
-        <v>208</v>
+        <v>289</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2291,13 +2834,13 @@
         <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E36">
         <v>0</v>
       </c>
       <c r="G36" t="s">
-        <v>209</v>
+        <v>290</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2311,16 +2854,16 @@
         <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E37">
         <v>0</v>
       </c>
       <c r="F37" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G37" t="s">
-        <v>210</v>
+        <v>291</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2334,13 +2877,13 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E38">
         <v>0</v>
       </c>
       <c r="G38" t="s">
-        <v>211</v>
+        <v>292</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2354,16 +2897,16 @@
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E39">
         <v>3389</v>
       </c>
       <c r="F39" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="G39" t="s">
-        <v>212</v>
+        <v>293</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2377,16 +2920,16 @@
         <v>16</v>
       </c>
       <c r="D40" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="G40" t="s">
-        <v>213</v>
+        <v>294</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2406,10 +2949,10 @@
         <v>3389</v>
       </c>
       <c r="F41" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="G41" t="s">
-        <v>214</v>
+        <v>295</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2429,10 +2972,10 @@
         <v>443</v>
       </c>
       <c r="F42" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G42" t="s">
-        <v>215</v>
+        <v>296</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2446,16 +2989,16 @@
         <v>16</v>
       </c>
       <c r="D43" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E43">
         <v>0</v>
       </c>
       <c r="F43" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G43" t="s">
-        <v>216</v>
+        <v>297</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2469,16 +3012,16 @@
         <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E44">
         <v>0</v>
       </c>
       <c r="F44" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G44" t="s">
-        <v>217</v>
+        <v>298</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2492,16 +3035,16 @@
         <v>17</v>
       </c>
       <c r="D45" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E45">
         <v>3389</v>
       </c>
       <c r="F45" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G45" t="s">
-        <v>218</v>
+        <v>299</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2515,16 +3058,16 @@
         <v>17</v>
       </c>
       <c r="D46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E46">
         <v>22</v>
       </c>
       <c r="F46" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G46" t="s">
-        <v>219</v>
+        <v>300</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -2538,16 +3081,16 @@
         <v>18</v>
       </c>
       <c r="D47" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E47">
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G47" t="s">
-        <v>220</v>
+        <v>301</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -2561,16 +3104,16 @@
         <v>15</v>
       </c>
       <c r="D48" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E48">
         <v>80</v>
       </c>
       <c r="F48" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G48" t="s">
-        <v>221</v>
+        <v>302</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2584,13 +3127,13 @@
         <v>16</v>
       </c>
       <c r="D49" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E49">
         <v>443</v>
       </c>
       <c r="G49" t="s">
-        <v>222</v>
+        <v>303</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2604,16 +3147,16 @@
         <v>17</v>
       </c>
       <c r="D50" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E50">
         <v>80</v>
       </c>
       <c r="F50" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G50" t="s">
-        <v>223</v>
+        <v>304</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2633,10 +3176,10 @@
         <v>443</v>
       </c>
       <c r="F51" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G51" t="s">
-        <v>224</v>
+        <v>305</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2650,13 +3193,13 @@
         <v>16</v>
       </c>
       <c r="D52" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E52">
         <v>0</v>
       </c>
       <c r="G52" t="s">
-        <v>225</v>
+        <v>306</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2670,16 +3213,16 @@
         <v>15</v>
       </c>
       <c r="D53" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E53">
         <v>0</v>
       </c>
       <c r="F53" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="G53" t="s">
-        <v>226</v>
+        <v>307</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2693,13 +3236,13 @@
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E54">
         <v>22</v>
       </c>
       <c r="G54" t="s">
-        <v>227</v>
+        <v>308</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2713,13 +3256,13 @@
         <v>15</v>
       </c>
       <c r="D55" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E55">
         <v>0</v>
       </c>
       <c r="G55" t="s">
-        <v>228</v>
+        <v>309</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2739,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="F56" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G56" t="s">
-        <v>229</v>
+        <v>310</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -2756,16 +3299,16 @@
         <v>15</v>
       </c>
       <c r="D57" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E57">
         <v>443</v>
       </c>
       <c r="F57" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="G57" t="s">
-        <v>230</v>
+        <v>311</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -2779,13 +3322,13 @@
         <v>17</v>
       </c>
       <c r="D58" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E58">
         <v>0</v>
       </c>
       <c r="G58" t="s">
-        <v>231</v>
+        <v>312</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2799,16 +3342,16 @@
         <v>16</v>
       </c>
       <c r="D59" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E59">
         <v>80</v>
       </c>
       <c r="F59" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="G59" t="s">
-        <v>232</v>
+        <v>313</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -2822,16 +3365,16 @@
         <v>16</v>
       </c>
       <c r="D60" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E60">
         <v>0</v>
       </c>
       <c r="F60" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="G60" t="s">
-        <v>233</v>
+        <v>314</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -2845,13 +3388,13 @@
         <v>15</v>
       </c>
       <c r="D61" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E61">
         <v>0</v>
       </c>
       <c r="G61" t="s">
-        <v>234</v>
+        <v>315</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2865,16 +3408,16 @@
         <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E62">
         <v>0</v>
       </c>
       <c r="F62" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G62" t="s">
-        <v>235</v>
+        <v>316</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2888,16 +3431,16 @@
         <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E63">
         <v>22</v>
       </c>
       <c r="F63" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G63" t="s">
-        <v>236</v>
+        <v>317</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2911,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="D64" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E64">
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>237</v>
+        <v>318</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -2931,16 +3474,16 @@
         <v>18</v>
       </c>
       <c r="D65" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E65">
         <v>22</v>
       </c>
       <c r="F65" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G65" t="s">
-        <v>238</v>
+        <v>319</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -2954,16 +3497,16 @@
         <v>17</v>
       </c>
       <c r="D66" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E66">
         <v>0</v>
       </c>
       <c r="F66" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G66" t="s">
-        <v>239</v>
+        <v>320</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -2977,16 +3520,16 @@
         <v>15</v>
       </c>
       <c r="D67" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E67">
         <v>3389</v>
       </c>
       <c r="F67" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G67" t="s">
-        <v>240</v>
+        <v>321</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3000,16 +3543,16 @@
         <v>16</v>
       </c>
       <c r="D68" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E68">
         <v>0</v>
       </c>
       <c r="F68" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G68" t="s">
-        <v>241</v>
+        <v>322</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3023,16 +3566,16 @@
         <v>15</v>
       </c>
       <c r="D69" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E69">
         <v>0</v>
       </c>
       <c r="F69" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G69" t="s">
-        <v>242</v>
+        <v>323</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3046,16 +3589,16 @@
         <v>17</v>
       </c>
       <c r="D70" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E70">
         <v>0</v>
       </c>
       <c r="F70" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G70" t="s">
-        <v>243</v>
+        <v>324</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3069,16 +3612,16 @@
         <v>15</v>
       </c>
       <c r="D71" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E71">
         <v>0</v>
       </c>
       <c r="F71" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G71" t="s">
-        <v>244</v>
+        <v>325</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3092,16 +3635,16 @@
         <v>17</v>
       </c>
       <c r="D72" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E72">
         <v>3389</v>
       </c>
       <c r="F72" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G72" t="s">
-        <v>245</v>
+        <v>326</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -3115,16 +3658,16 @@
         <v>16</v>
       </c>
       <c r="D73" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E73">
         <v>0</v>
       </c>
       <c r="F73" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G73" t="s">
-        <v>246</v>
+        <v>327</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3138,16 +3681,16 @@
         <v>18</v>
       </c>
       <c r="D74" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E74">
         <v>0</v>
       </c>
       <c r="F74" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="G74" t="s">
-        <v>247</v>
+        <v>328</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -3161,16 +3704,16 @@
         <v>17</v>
       </c>
       <c r="D75" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E75">
         <v>0</v>
       </c>
       <c r="F75" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G75" t="s">
-        <v>248</v>
+        <v>329</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3184,16 +3727,16 @@
         <v>16</v>
       </c>
       <c r="D76" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E76">
         <v>3389</v>
       </c>
       <c r="F76" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="G76" t="s">
-        <v>249</v>
+        <v>330</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -3207,16 +3750,16 @@
         <v>18</v>
       </c>
       <c r="D77" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E77">
         <v>0</v>
       </c>
       <c r="F77" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G77" t="s">
-        <v>250</v>
+        <v>331</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -3230,13 +3773,13 @@
         <v>17</v>
       </c>
       <c r="D78" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E78">
         <v>0</v>
       </c>
       <c r="G78" t="s">
-        <v>251</v>
+        <v>332</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -3250,16 +3793,16 @@
         <v>18</v>
       </c>
       <c r="D79" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E79">
         <v>0</v>
       </c>
       <c r="F79" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G79" t="s">
-        <v>252</v>
+        <v>333</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -3273,16 +3816,16 @@
         <v>16</v>
       </c>
       <c r="D80" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E80">
         <v>0</v>
       </c>
       <c r="F80" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G80" t="s">
-        <v>253</v>
+        <v>334</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -3296,13 +3839,13 @@
         <v>15</v>
       </c>
       <c r="D81" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E81">
         <v>0</v>
       </c>
       <c r="G81" t="s">
-        <v>254</v>
+        <v>335</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -3316,16 +3859,16 @@
         <v>16</v>
       </c>
       <c r="D82" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E82">
         <v>0</v>
       </c>
       <c r="F82" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="G82" t="s">
-        <v>255</v>
+        <v>336</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -3339,13 +3882,13 @@
         <v>18</v>
       </c>
       <c r="D83" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E83">
         <v>0</v>
       </c>
       <c r="G83" t="s">
-        <v>256</v>
+        <v>337</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -3359,16 +3902,16 @@
         <v>17</v>
       </c>
       <c r="D84" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E84">
         <v>0</v>
       </c>
       <c r="F84" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G84" t="s">
-        <v>257</v>
+        <v>338</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -3382,16 +3925,16 @@
         <v>18</v>
       </c>
       <c r="D85" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E85">
         <v>0</v>
       </c>
       <c r="F85" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="G85" t="s">
-        <v>258</v>
+        <v>339</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -3405,16 +3948,16 @@
         <v>16</v>
       </c>
       <c r="D86" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E86">
         <v>443</v>
       </c>
       <c r="F86" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G86" t="s">
-        <v>259</v>
+        <v>340</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -3434,10 +3977,10 @@
         <v>22</v>
       </c>
       <c r="F87" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="G87" t="s">
-        <v>260</v>
+        <v>341</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -3451,13 +3994,13 @@
         <v>16</v>
       </c>
       <c r="D88" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E88">
         <v>443</v>
       </c>
       <c r="G88" t="s">
-        <v>261</v>
+        <v>342</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -3471,16 +4014,16 @@
         <v>16</v>
       </c>
       <c r="D89" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E89">
         <v>0</v>
       </c>
       <c r="F89" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G89" t="s">
-        <v>262</v>
+        <v>343</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3494,16 +4037,16 @@
         <v>17</v>
       </c>
       <c r="D90" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E90">
         <v>0</v>
       </c>
       <c r="F90" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="G90" t="s">
-        <v>263</v>
+        <v>344</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -3517,16 +4060,16 @@
         <v>15</v>
       </c>
       <c r="D91" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E91">
         <v>0</v>
       </c>
       <c r="F91" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G91" t="s">
-        <v>264</v>
+        <v>345</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -3540,16 +4083,16 @@
         <v>15</v>
       </c>
       <c r="D92" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E92">
         <v>3389</v>
       </c>
       <c r="F92" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G92" t="s">
-        <v>265</v>
+        <v>346</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -3563,16 +4106,16 @@
         <v>15</v>
       </c>
       <c r="D93" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E93">
         <v>0</v>
       </c>
       <c r="F93" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="G93" t="s">
-        <v>266</v>
+        <v>347</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -3586,16 +4129,16 @@
         <v>17</v>
       </c>
       <c r="D94" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E94">
         <v>0</v>
       </c>
       <c r="F94" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="G94" t="s">
-        <v>267</v>
+        <v>348</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -3609,16 +4152,16 @@
         <v>16</v>
       </c>
       <c r="D95" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E95">
         <v>0</v>
       </c>
       <c r="F95" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="G95" t="s">
-        <v>268</v>
+        <v>349</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -3632,16 +4175,16 @@
         <v>18</v>
       </c>
       <c r="D96" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E96">
         <v>22</v>
       </c>
       <c r="F96" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="G96" t="s">
-        <v>269</v>
+        <v>350</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -3655,16 +4198,16 @@
         <v>15</v>
       </c>
       <c r="D97" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E97">
         <v>0</v>
       </c>
       <c r="F97" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="G97" t="s">
-        <v>270</v>
+        <v>351</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -3684,10 +4227,10 @@
         <v>0</v>
       </c>
       <c r="F98" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="G98" t="s">
-        <v>271</v>
+        <v>352</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -3701,16 +4244,16 @@
         <v>16</v>
       </c>
       <c r="D99" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E99">
         <v>3389</v>
       </c>
       <c r="F99" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="G99" t="s">
-        <v>272</v>
+        <v>353</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -3724,16 +4267,16 @@
         <v>18</v>
       </c>
       <c r="D100" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E100">
         <v>0</v>
       </c>
       <c r="F100" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="G100" t="s">
-        <v>273</v>
+        <v>354</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -3747,16 +4290,16 @@
         <v>15</v>
       </c>
       <c r="D101" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E101">
         <v>22</v>
       </c>
       <c r="F101" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G101" t="s">
-        <v>274</v>
+        <v>355</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -3770,16 +4313,16 @@
         <v>16</v>
       </c>
       <c r="D102" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E102">
         <v>3389</v>
       </c>
       <c r="F102" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="G102" t="s">
-        <v>275</v>
+        <v>356</v>
       </c>
     </row>
     <row r="103" spans="1:7">
@@ -3799,10 +4342,10 @@
         <v>0</v>
       </c>
       <c r="F103" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="G103" t="s">
-        <v>276</v>
+        <v>357</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -3816,16 +4359,16 @@
         <v>18</v>
       </c>
       <c r="D104" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E104">
         <v>3389</v>
       </c>
       <c r="F104" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="G104" t="s">
-        <v>277</v>
+        <v>358</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -3839,16 +4382,16 @@
         <v>17</v>
       </c>
       <c r="D105" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E105">
         <v>443</v>
       </c>
       <c r="F105" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="G105" t="s">
-        <v>278</v>
+        <v>359</v>
       </c>
     </row>
     <row r="106" spans="1:7">
@@ -3862,13 +4405,13 @@
         <v>18</v>
       </c>
       <c r="D106" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E106">
         <v>22</v>
       </c>
       <c r="G106" t="s">
-        <v>279</v>
+        <v>360</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -3882,13 +4425,13 @@
         <v>18</v>
       </c>
       <c r="D107" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E107">
         <v>80</v>
       </c>
       <c r="G107" t="s">
-        <v>280</v>
+        <v>361</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -3902,16 +4445,16 @@
         <v>17</v>
       </c>
       <c r="D108" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E108">
         <v>0</v>
       </c>
       <c r="F108" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="G108" t="s">
-        <v>281</v>
+        <v>362</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -3925,16 +4468,16 @@
         <v>18</v>
       </c>
       <c r="D109" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E109">
         <v>80</v>
       </c>
       <c r="F109" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="G109" t="s">
-        <v>282</v>
+        <v>363</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -3948,13 +4491,13 @@
         <v>17</v>
       </c>
       <c r="D110" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E110">
         <v>0</v>
       </c>
       <c r="G110" t="s">
-        <v>283</v>
+        <v>364</v>
       </c>
     </row>
     <row r="111" spans="1:7">
@@ -3968,16 +4511,16 @@
         <v>15</v>
       </c>
       <c r="D111" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E111">
         <v>0</v>
       </c>
       <c r="F111" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="G111" t="s">
-        <v>284</v>
+        <v>365</v>
       </c>
     </row>
     <row r="112" spans="1:7">
@@ -3991,16 +4534,16 @@
         <v>18</v>
       </c>
       <c r="D112" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E112">
         <v>0</v>
       </c>
       <c r="F112" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G112" t="s">
-        <v>285</v>
+        <v>366</v>
       </c>
     </row>
     <row r="113" spans="1:7">
@@ -4014,16 +4557,16 @@
         <v>17</v>
       </c>
       <c r="D113" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E113">
         <v>0</v>
       </c>
       <c r="F113" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="G113" t="s">
-        <v>286</v>
+        <v>367</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4037,16 +4580,16 @@
         <v>15</v>
       </c>
       <c r="D114" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E114">
         <v>0</v>
       </c>
       <c r="F114" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G114" t="s">
-        <v>287</v>
+        <v>368</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4060,16 +4603,16 @@
         <v>18</v>
       </c>
       <c r="D115" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E115">
         <v>22</v>
       </c>
       <c r="F115" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="G115" t="s">
-        <v>288</v>
+        <v>369</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4083,16 +4626,16 @@
         <v>16</v>
       </c>
       <c r="D116" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E116">
         <v>80</v>
       </c>
       <c r="F116" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G116" t="s">
-        <v>289</v>
+        <v>370</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4106,16 +4649,16 @@
         <v>18</v>
       </c>
       <c r="D117" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E117">
         <v>0</v>
       </c>
       <c r="F117" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="G117" t="s">
-        <v>290</v>
+        <v>371</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4135,10 +4678,10 @@
         <v>0</v>
       </c>
       <c r="F118" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="G118" t="s">
-        <v>291</v>
+        <v>372</v>
       </c>
     </row>
     <row r="119" spans="1:7">
@@ -4152,16 +4695,16 @@
         <v>17</v>
       </c>
       <c r="D119" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E119">
         <v>0</v>
       </c>
       <c r="F119" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="G119" t="s">
-        <v>292</v>
+        <v>373</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -4175,13 +4718,13 @@
         <v>16</v>
       </c>
       <c r="D120" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E120">
         <v>443</v>
       </c>
       <c r="G120" t="s">
-        <v>293</v>
+        <v>374</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4195,13 +4738,13 @@
         <v>16</v>
       </c>
       <c r="D121" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E121">
         <v>443</v>
       </c>
       <c r="G121" t="s">
-        <v>294</v>
+        <v>375</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4215,16 +4758,16 @@
         <v>16</v>
       </c>
       <c r="D122" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E122">
         <v>0</v>
       </c>
       <c r="F122" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="G122" t="s">
-        <v>295</v>
+        <v>376</v>
       </c>
     </row>
     <row r="123" spans="1:7">
@@ -4238,16 +4781,16 @@
         <v>15</v>
       </c>
       <c r="D123" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E123">
         <v>0</v>
       </c>
       <c r="F123" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="G123" t="s">
-        <v>296</v>
+        <v>377</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4261,13 +4804,13 @@
         <v>16</v>
       </c>
       <c r="D124" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E124">
         <v>0</v>
       </c>
       <c r="G124" t="s">
-        <v>297</v>
+        <v>378</v>
       </c>
     </row>
     <row r="125" spans="1:7">
@@ -4281,16 +4824,16 @@
         <v>16</v>
       </c>
       <c r="D125" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E125">
         <v>0</v>
       </c>
       <c r="F125" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="G125" t="s">
-        <v>298</v>
+        <v>379</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4310,10 +4853,10 @@
         <v>0</v>
       </c>
       <c r="F126" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="G126" t="s">
-        <v>299</v>
+        <v>380</v>
       </c>
     </row>
     <row r="127" spans="1:7">
@@ -4333,10 +4876,10 @@
         <v>0</v>
       </c>
       <c r="F127" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G127" t="s">
-        <v>300</v>
+        <v>381</v>
       </c>
     </row>
     <row r="128" spans="1:7">
@@ -4350,13 +4893,13 @@
         <v>15</v>
       </c>
       <c r="D128" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E128">
         <v>80</v>
       </c>
       <c r="G128" t="s">
-        <v>301</v>
+        <v>382</v>
       </c>
     </row>
     <row r="129" spans="1:7">
@@ -4370,16 +4913,16 @@
         <v>16</v>
       </c>
       <c r="D129" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E129">
         <v>0</v>
       </c>
       <c r="F129" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="G129" t="s">
-        <v>302</v>
+        <v>383</v>
       </c>
     </row>
     <row r="130" spans="1:7">
@@ -4393,16 +4936,16 @@
         <v>17</v>
       </c>
       <c r="D130" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E130">
         <v>0</v>
       </c>
       <c r="F130" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="G130" t="s">
-        <v>303</v>
+        <v>384</v>
       </c>
     </row>
     <row r="131" spans="1:7">
@@ -4416,16 +4959,16 @@
         <v>15</v>
       </c>
       <c r="D131" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E131">
         <v>0</v>
       </c>
       <c r="F131" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="G131" t="s">
-        <v>304</v>
+        <v>385</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4439,16 +4982,16 @@
         <v>16</v>
       </c>
       <c r="D132" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E132">
         <v>22</v>
       </c>
       <c r="F132" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G132" t="s">
-        <v>305</v>
+        <v>386</v>
       </c>
     </row>
     <row r="133" spans="1:7">
@@ -4462,13 +5005,13 @@
         <v>16</v>
       </c>
       <c r="D133" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E133">
         <v>22</v>
       </c>
       <c r="G133" t="s">
-        <v>306</v>
+        <v>387</v>
       </c>
     </row>
     <row r="134" spans="1:7">
@@ -4482,13 +5025,13 @@
         <v>18</v>
       </c>
       <c r="D134" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E134">
         <v>443</v>
       </c>
       <c r="G134" t="s">
-        <v>307</v>
+        <v>388</v>
       </c>
     </row>
     <row r="135" spans="1:7">
@@ -4502,16 +5045,16 @@
         <v>15</v>
       </c>
       <c r="D135" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E135">
         <v>0</v>
       </c>
       <c r="F135" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="G135" t="s">
-        <v>308</v>
+        <v>389</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4525,13 +5068,13 @@
         <v>15</v>
       </c>
       <c r="D136" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E136">
         <v>0</v>
       </c>
       <c r="G136" t="s">
-        <v>309</v>
+        <v>390</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -4545,16 +5088,16 @@
         <v>15</v>
       </c>
       <c r="D137" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E137">
         <v>0</v>
       </c>
       <c r="F137" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="G137" t="s">
-        <v>310</v>
+        <v>391</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -4568,16 +5111,16 @@
         <v>15</v>
       </c>
       <c r="D138" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E138">
         <v>0</v>
       </c>
       <c r="F138" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G138" t="s">
-        <v>311</v>
+        <v>392</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -4591,16 +5134,16 @@
         <v>15</v>
       </c>
       <c r="D139" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E139">
         <v>80</v>
       </c>
       <c r="F139" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="G139" t="s">
-        <v>312</v>
+        <v>393</v>
       </c>
     </row>
     <row r="140" spans="1:7">
@@ -4614,16 +5157,16 @@
         <v>17</v>
       </c>
       <c r="D140" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E140">
         <v>80</v>
       </c>
       <c r="F140" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="G140" t="s">
-        <v>313</v>
+        <v>394</v>
       </c>
     </row>
     <row r="141" spans="1:7">
@@ -4637,13 +5180,13 @@
         <v>18</v>
       </c>
       <c r="D141" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E141">
         <v>0</v>
       </c>
       <c r="G141" t="s">
-        <v>314</v>
+        <v>395</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -4657,13 +5200,13 @@
         <v>17</v>
       </c>
       <c r="D142" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E142">
         <v>22</v>
       </c>
       <c r="G142" t="s">
-        <v>315</v>
+        <v>396</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -4677,16 +5220,16 @@
         <v>18</v>
       </c>
       <c r="D143" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E143">
         <v>0</v>
       </c>
       <c r="F143" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="G143" t="s">
-        <v>316</v>
+        <v>397</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -4700,13 +5243,13 @@
         <v>18</v>
       </c>
       <c r="D144" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E144">
         <v>0</v>
       </c>
       <c r="G144" t="s">
-        <v>317</v>
+        <v>398</v>
       </c>
     </row>
     <row r="145" spans="1:7">
@@ -4720,16 +5263,16 @@
         <v>15</v>
       </c>
       <c r="D145" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E145">
         <v>0</v>
       </c>
       <c r="F145" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="G145" t="s">
-        <v>318</v>
+        <v>399</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -4743,16 +5286,16 @@
         <v>17</v>
       </c>
       <c r="D146" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E146">
         <v>0</v>
       </c>
       <c r="F146" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="G146" t="s">
-        <v>319</v>
+        <v>400</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -4766,16 +5309,16 @@
         <v>16</v>
       </c>
       <c r="D147" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E147">
         <v>0</v>
       </c>
       <c r="F147" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="G147" t="s">
-        <v>320</v>
+        <v>401</v>
       </c>
     </row>
     <row r="148" spans="1:7">
@@ -4789,16 +5332,16 @@
         <v>16</v>
       </c>
       <c r="D148" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E148">
         <v>443</v>
       </c>
       <c r="F148" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G148" t="s">
-        <v>321</v>
+        <v>402</v>
       </c>
     </row>
     <row r="149" spans="1:7">
@@ -4812,16 +5355,16 @@
         <v>15</v>
       </c>
       <c r="D149" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E149">
         <v>0</v>
       </c>
       <c r="F149" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="G149" t="s">
-        <v>322</v>
+        <v>403</v>
       </c>
     </row>
     <row r="150" spans="1:7">
@@ -4835,16 +5378,16 @@
         <v>17</v>
       </c>
       <c r="D150" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E150">
         <v>0</v>
       </c>
       <c r="F150" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="G150" t="s">
-        <v>323</v>
+        <v>404</v>
       </c>
     </row>
     <row r="151" spans="1:7">
@@ -4858,16 +5401,16 @@
         <v>16</v>
       </c>
       <c r="D151" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E151">
         <v>3389</v>
       </c>
       <c r="F151" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="G151" t="s">
-        <v>324</v>
+        <v>405</v>
       </c>
     </row>
     <row r="152" spans="1:7">
@@ -4881,16 +5424,16 @@
         <v>16</v>
       </c>
       <c r="D152" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E152">
         <v>0</v>
       </c>
       <c r="F152" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="G152" t="s">
-        <v>325</v>
+        <v>406</v>
       </c>
     </row>
     <row r="153" spans="1:7">
@@ -4904,16 +5447,16 @@
         <v>16</v>
       </c>
       <c r="D153" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E153">
         <v>80</v>
       </c>
       <c r="F153" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="G153" t="s">
-        <v>326</v>
+        <v>407</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -4927,16 +5470,16 @@
         <v>15</v>
       </c>
       <c r="D154" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E154">
         <v>80</v>
       </c>
       <c r="F154" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="G154" t="s">
-        <v>327</v>
+        <v>408</v>
       </c>
     </row>
     <row r="155" spans="1:7">
@@ -4956,10 +5499,10 @@
         <v>0</v>
       </c>
       <c r="F155" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="G155" t="s">
-        <v>328</v>
+        <v>409</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -4973,16 +5516,16 @@
         <v>18</v>
       </c>
       <c r="D156" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E156">
         <v>0</v>
       </c>
       <c r="F156" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="G156" t="s">
-        <v>329</v>
+        <v>410</v>
       </c>
     </row>
     <row r="157" spans="1:7">
@@ -4996,16 +5539,16 @@
         <v>18</v>
       </c>
       <c r="D157" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E157">
         <v>0</v>
       </c>
       <c r="F157" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="G157" t="s">
-        <v>330</v>
+        <v>411</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5019,13 +5562,13 @@
         <v>16</v>
       </c>
       <c r="D158" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E158">
         <v>0</v>
       </c>
       <c r="G158" t="s">
-        <v>331</v>
+        <v>412</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5039,16 +5582,16 @@
         <v>18</v>
       </c>
       <c r="D159" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E159">
         <v>3389</v>
       </c>
       <c r="F159" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="G159" t="s">
-        <v>332</v>
+        <v>413</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5062,13 +5605,13 @@
         <v>16</v>
       </c>
       <c r="D160" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E160">
         <v>0</v>
       </c>
       <c r="G160" t="s">
-        <v>333</v>
+        <v>414</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5082,16 +5625,16 @@
         <v>18</v>
       </c>
       <c r="D161" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E161">
         <v>3389</v>
       </c>
       <c r="F161" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="G161" t="s">
-        <v>334</v>
+        <v>415</v>
       </c>
     </row>
     <row r="162" spans="1:7">
@@ -5111,10 +5654,10 @@
         <v>22</v>
       </c>
       <c r="F162" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="G162" t="s">
-        <v>335</v>
+        <v>416</v>
       </c>
     </row>
     <row r="163" spans="1:7">
@@ -5128,13 +5671,13 @@
         <v>18</v>
       </c>
       <c r="D163" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E163">
         <v>443</v>
       </c>
       <c r="G163" t="s">
-        <v>336</v>
+        <v>417</v>
       </c>
     </row>
     <row r="164" spans="1:7">
@@ -5148,16 +5691,16 @@
         <v>18</v>
       </c>
       <c r="D164" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E164">
         <v>0</v>
       </c>
       <c r="F164" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G164" t="s">
-        <v>337</v>
+        <v>418</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5171,16 +5714,16 @@
         <v>18</v>
       </c>
       <c r="D165" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E165">
         <v>0</v>
       </c>
       <c r="F165" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="G165" t="s">
-        <v>338</v>
+        <v>419</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5194,16 +5737,16 @@
         <v>15</v>
       </c>
       <c r="D166" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E166">
         <v>0</v>
       </c>
       <c r="F166" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="G166" t="s">
-        <v>339</v>
+        <v>420</v>
       </c>
     </row>
     <row r="167" spans="1:7">
@@ -5217,16 +5760,16 @@
         <v>16</v>
       </c>
       <c r="D167" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E167">
         <v>0</v>
       </c>
       <c r="F167" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="G167" t="s">
-        <v>340</v>
+        <v>421</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5246,10 +5789,10 @@
         <v>22</v>
       </c>
       <c r="F168" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G168" t="s">
-        <v>341</v>
+        <v>422</v>
       </c>
     </row>
     <row r="169" spans="1:7">
@@ -5263,16 +5806,16 @@
         <v>16</v>
       </c>
       <c r="D169" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E169">
         <v>443</v>
       </c>
       <c r="F169" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="G169" t="s">
-        <v>342</v>
+        <v>423</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5286,16 +5829,16 @@
         <v>16</v>
       </c>
       <c r="D170" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E170">
         <v>80</v>
       </c>
       <c r="F170" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="G170" t="s">
-        <v>343</v>
+        <v>424</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5309,13 +5852,13 @@
         <v>16</v>
       </c>
       <c r="D171" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E171">
         <v>0</v>
       </c>
       <c r="G171" t="s">
-        <v>344</v>
+        <v>425</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5329,13 +5872,13 @@
         <v>15</v>
       </c>
       <c r="D172" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E172">
         <v>3389</v>
       </c>
       <c r="G172" t="s">
-        <v>345</v>
+        <v>426</v>
       </c>
     </row>
     <row r="173" spans="1:7">
@@ -5349,13 +5892,13 @@
         <v>17</v>
       </c>
       <c r="D173" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E173">
         <v>0</v>
       </c>
       <c r="G173" t="s">
-        <v>346</v>
+        <v>427</v>
       </c>
     </row>
     <row r="174" spans="1:7">
@@ -5369,13 +5912,13 @@
         <v>15</v>
       </c>
       <c r="D174" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E174">
         <v>443</v>
       </c>
       <c r="G174" t="s">
-        <v>347</v>
+        <v>428</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5389,13 +5932,13 @@
         <v>17</v>
       </c>
       <c r="D175" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E175">
         <v>0</v>
       </c>
       <c r="G175" t="s">
-        <v>348</v>
+        <v>429</v>
       </c>
     </row>
     <row r="176" spans="1:7">
@@ -5409,16 +5952,16 @@
         <v>15</v>
       </c>
       <c r="D176" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E176">
         <v>80</v>
       </c>
       <c r="F176" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="G176" t="s">
-        <v>349</v>
+        <v>430</v>
       </c>
     </row>
     <row r="177" spans="1:7">
@@ -5432,16 +5975,16 @@
         <v>17</v>
       </c>
       <c r="D177" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E177">
         <v>0</v>
       </c>
       <c r="F177" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="G177" t="s">
-        <v>350</v>
+        <v>431</v>
       </c>
     </row>
     <row r="178" spans="1:7">
@@ -5455,16 +5998,16 @@
         <v>18</v>
       </c>
       <c r="D178" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="E178">
         <v>0</v>
       </c>
       <c r="F178" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="G178" t="s">
-        <v>351</v>
+        <v>432</v>
       </c>
     </row>
     <row r="179" spans="1:7">
@@ -5478,16 +6021,16 @@
         <v>17</v>
       </c>
       <c r="D179" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E179">
         <v>0</v>
       </c>
       <c r="F179" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="G179" t="s">
-        <v>352</v>
+        <v>433</v>
       </c>
     </row>
     <row r="180" spans="1:7">
@@ -5501,16 +6044,16 @@
         <v>18</v>
       </c>
       <c r="D180" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E180">
         <v>80</v>
       </c>
       <c r="F180" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="G180" t="s">
-        <v>353</v>
+        <v>434</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5524,16 +6067,16 @@
         <v>15</v>
       </c>
       <c r="D181" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E181">
         <v>80</v>
       </c>
       <c r="F181" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="G181" t="s">
-        <v>354</v>
+        <v>435</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5547,13 +6090,13 @@
         <v>16</v>
       </c>
       <c r="D182" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E182">
         <v>443</v>
       </c>
       <c r="G182" t="s">
-        <v>355</v>
+        <v>436</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5567,13 +6110,13 @@
         <v>18</v>
       </c>
       <c r="D183" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E183">
         <v>0</v>
       </c>
       <c r="G183" t="s">
-        <v>356</v>
+        <v>437</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5587,13 +6130,13 @@
         <v>16</v>
       </c>
       <c r="D184" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="E184">
         <v>0</v>
       </c>
       <c r="G184" t="s">
-        <v>357</v>
+        <v>438</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -5607,16 +6150,16 @@
         <v>16</v>
       </c>
       <c r="D185" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E185">
         <v>0</v>
       </c>
       <c r="F185" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="G185" t="s">
-        <v>358</v>
+        <v>439</v>
       </c>
     </row>
     <row r="186" spans="1:7">
@@ -5630,13 +6173,13 @@
         <v>16</v>
       </c>
       <c r="D186" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E186">
         <v>0</v>
       </c>
       <c r="G186" t="s">
-        <v>359</v>
+        <v>440</v>
       </c>
     </row>
     <row r="187" spans="1:7">
@@ -5656,10 +6199,10 @@
         <v>0</v>
       </c>
       <c r="F187" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="G187" t="s">
-        <v>360</v>
+        <v>441</v>
       </c>
     </row>
     <row r="188" spans="1:7">
@@ -5673,16 +6216,16 @@
         <v>16</v>
       </c>
       <c r="D188" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E188">
         <v>0</v>
       </c>
       <c r="F188" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="G188" t="s">
-        <v>361</v>
+        <v>442</v>
       </c>
     </row>
     <row r="189" spans="1:7">
@@ -5696,16 +6239,16 @@
         <v>15</v>
       </c>
       <c r="D189" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E189">
         <v>0</v>
       </c>
       <c r="F189" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="G189" t="s">
-        <v>362</v>
+        <v>443</v>
       </c>
     </row>
     <row r="190" spans="1:7">
@@ -5719,16 +6262,16 @@
         <v>17</v>
       </c>
       <c r="D190" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E190">
         <v>0</v>
       </c>
       <c r="F190" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="G190" t="s">
-        <v>363</v>
+        <v>444</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -5742,16 +6285,16 @@
         <v>15</v>
       </c>
       <c r="D191" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E191">
         <v>0</v>
       </c>
       <c r="F191" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="G191" t="s">
-        <v>364</v>
+        <v>445</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -5765,13 +6308,13 @@
         <v>16</v>
       </c>
       <c r="D192" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E192">
         <v>0</v>
       </c>
       <c r="G192" t="s">
-        <v>365</v>
+        <v>446</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -5785,13 +6328,13 @@
         <v>15</v>
       </c>
       <c r="D193" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E193">
         <v>0</v>
       </c>
       <c r="G193" t="s">
-        <v>366</v>
+        <v>447</v>
       </c>
     </row>
     <row r="194" spans="1:7">
@@ -5805,16 +6348,16 @@
         <v>15</v>
       </c>
       <c r="D194" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E194">
         <v>3389</v>
       </c>
       <c r="F194" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="G194" t="s">
-        <v>367</v>
+        <v>448</v>
       </c>
     </row>
     <row r="195" spans="1:7">
@@ -5828,16 +6371,16 @@
         <v>16</v>
       </c>
       <c r="D195" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E195">
         <v>0</v>
       </c>
       <c r="F195" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="G195" t="s">
-        <v>368</v>
+        <v>449</v>
       </c>
     </row>
     <row r="196" spans="1:7">
@@ -5851,16 +6394,16 @@
         <v>17</v>
       </c>
       <c r="D196" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E196">
         <v>0</v>
       </c>
       <c r="F196" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="G196" t="s">
-        <v>369</v>
+        <v>450</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -5880,10 +6423,10 @@
         <v>3389</v>
       </c>
       <c r="F197" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="G197" t="s">
-        <v>370</v>
+        <v>451</v>
       </c>
     </row>
     <row r="198" spans="1:7">
@@ -5897,16 +6440,16 @@
         <v>15</v>
       </c>
       <c r="D198" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E198">
         <v>0</v>
       </c>
       <c r="F198" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G198" t="s">
-        <v>371</v>
+        <v>452</v>
       </c>
     </row>
     <row r="199" spans="1:7">
@@ -5920,16 +6463,16 @@
         <v>15</v>
       </c>
       <c r="D199" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E199">
         <v>0</v>
       </c>
       <c r="F199" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="G199" t="s">
-        <v>372</v>
+        <v>453</v>
       </c>
     </row>
     <row r="200" spans="1:7">
@@ -5949,7 +6492,7 @@
         <v>0</v>
       </c>
       <c r="G200" t="s">
-        <v>373</v>
+        <v>454</v>
       </c>
     </row>
     <row r="201" spans="1:7">
@@ -5963,16 +6506,1938 @@
         <v>17</v>
       </c>
       <c r="D201" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E201">
         <v>443</v>
       </c>
       <c r="F201" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="G201" t="s">
-        <v>374</v>
+        <v>455</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7">
+      <c r="A202">
+        <v>6450</v>
+      </c>
+      <c r="B202" t="s">
+        <v>12</v>
+      </c>
+      <c r="C202" t="s">
+        <v>16</v>
+      </c>
+      <c r="D202" t="s">
+        <v>21</v>
+      </c>
+      <c r="F202" t="s">
+        <v>182</v>
+      </c>
+      <c r="G202" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7">
+      <c r="A203">
+        <v>2168</v>
+      </c>
+      <c r="B203" t="s">
+        <v>7</v>
+      </c>
+      <c r="C203" t="s">
+        <v>15</v>
+      </c>
+      <c r="D203" t="s">
+        <v>27</v>
+      </c>
+      <c r="G203" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7">
+      <c r="A204">
+        <v>3265</v>
+      </c>
+      <c r="B204" t="s">
+        <v>8</v>
+      </c>
+      <c r="C204" t="s">
+        <v>15</v>
+      </c>
+      <c r="D204" t="s">
+        <v>27</v>
+      </c>
+      <c r="F204" t="s">
+        <v>183</v>
+      </c>
+      <c r="G204" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7">
+      <c r="A205">
+        <v>2905</v>
+      </c>
+      <c r="B205" t="s">
+        <v>7</v>
+      </c>
+      <c r="C205" t="s">
+        <v>15</v>
+      </c>
+      <c r="D205" t="s">
+        <v>30</v>
+      </c>
+      <c r="F205" t="s">
+        <v>184</v>
+      </c>
+      <c r="G205" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7">
+      <c r="A206">
+        <v>7015</v>
+      </c>
+      <c r="B206" t="s">
+        <v>11</v>
+      </c>
+      <c r="C206" t="s">
+        <v>16</v>
+      </c>
+      <c r="D206" t="s">
+        <v>29</v>
+      </c>
+      <c r="G206" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7">
+      <c r="A207">
+        <v>9020</v>
+      </c>
+      <c r="B207" t="s">
+        <v>9</v>
+      </c>
+      <c r="C207" t="s">
+        <v>15</v>
+      </c>
+      <c r="D207" t="s">
+        <v>29</v>
+      </c>
+      <c r="F207" t="s">
+        <v>185</v>
+      </c>
+      <c r="G207" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7">
+      <c r="A208">
+        <v>5894</v>
+      </c>
+      <c r="B208" t="s">
+        <v>13</v>
+      </c>
+      <c r="C208" t="s">
+        <v>16</v>
+      </c>
+      <c r="D208" t="s">
+        <v>19</v>
+      </c>
+      <c r="F208" t="s">
+        <v>186</v>
+      </c>
+      <c r="G208" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7">
+      <c r="A209">
+        <v>6765</v>
+      </c>
+      <c r="B209" t="s">
+        <v>7</v>
+      </c>
+      <c r="C209" t="s">
+        <v>16</v>
+      </c>
+      <c r="D209" t="s">
+        <v>20</v>
+      </c>
+      <c r="F209" t="s">
+        <v>187</v>
+      </c>
+      <c r="G209" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7">
+      <c r="A210">
+        <v>6884</v>
+      </c>
+      <c r="B210" t="s">
+        <v>12</v>
+      </c>
+      <c r="C210" t="s">
+        <v>17</v>
+      </c>
+      <c r="D210" t="s">
+        <v>19</v>
+      </c>
+      <c r="F210" t="s">
+        <v>188</v>
+      </c>
+      <c r="G210" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7">
+      <c r="A211">
+        <v>6716</v>
+      </c>
+      <c r="B211" t="s">
+        <v>9</v>
+      </c>
+      <c r="C211" t="s">
+        <v>15</v>
+      </c>
+      <c r="D211" t="s">
+        <v>29</v>
+      </c>
+      <c r="F211" t="s">
+        <v>189</v>
+      </c>
+      <c r="G211" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7">
+      <c r="A212">
+        <v>8857</v>
+      </c>
+      <c r="B212" t="s">
+        <v>14</v>
+      </c>
+      <c r="C212" t="s">
+        <v>18</v>
+      </c>
+      <c r="D212" t="s">
+        <v>20</v>
+      </c>
+      <c r="F212" t="s">
+        <v>190</v>
+      </c>
+      <c r="G212" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7">
+      <c r="A213">
+        <v>7239</v>
+      </c>
+      <c r="B213" t="s">
+        <v>8</v>
+      </c>
+      <c r="C213" t="s">
+        <v>15</v>
+      </c>
+      <c r="D213" t="s">
+        <v>21</v>
+      </c>
+      <c r="G213" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7">
+      <c r="A214">
+        <v>4723</v>
+      </c>
+      <c r="B214" t="s">
+        <v>9</v>
+      </c>
+      <c r="C214" t="s">
+        <v>17</v>
+      </c>
+      <c r="D214" t="s">
+        <v>23</v>
+      </c>
+      <c r="F214" t="s">
+        <v>191</v>
+      </c>
+      <c r="G214" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7">
+      <c r="A215">
+        <v>6768</v>
+      </c>
+      <c r="B215" t="s">
+        <v>11</v>
+      </c>
+      <c r="C215" t="s">
+        <v>17</v>
+      </c>
+      <c r="D215" t="s">
+        <v>28</v>
+      </c>
+      <c r="F215" t="s">
+        <v>192</v>
+      </c>
+      <c r="G215" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7">
+      <c r="A216">
+        <v>5718</v>
+      </c>
+      <c r="B216" t="s">
+        <v>7</v>
+      </c>
+      <c r="C216" t="s">
+        <v>16</v>
+      </c>
+      <c r="D216" t="s">
+        <v>19</v>
+      </c>
+      <c r="F216" t="s">
+        <v>193</v>
+      </c>
+      <c r="G216" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7">
+      <c r="A217">
+        <v>6241</v>
+      </c>
+      <c r="B217" t="s">
+        <v>10</v>
+      </c>
+      <c r="C217" t="s">
+        <v>15</v>
+      </c>
+      <c r="D217" t="s">
+        <v>30</v>
+      </c>
+      <c r="G217" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7">
+      <c r="A218">
+        <v>8518</v>
+      </c>
+      <c r="B218" t="s">
+        <v>9</v>
+      </c>
+      <c r="C218" t="s">
+        <v>17</v>
+      </c>
+      <c r="D218" t="s">
+        <v>21</v>
+      </c>
+      <c r="G218" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7">
+      <c r="A219">
+        <v>1897</v>
+      </c>
+      <c r="B219" t="s">
+        <v>8</v>
+      </c>
+      <c r="C219" t="s">
+        <v>16</v>
+      </c>
+      <c r="D219" t="s">
+        <v>29</v>
+      </c>
+      <c r="F219" t="s">
+        <v>194</v>
+      </c>
+      <c r="G219" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7">
+      <c r="A220">
+        <v>6685</v>
+      </c>
+      <c r="B220" t="s">
+        <v>7</v>
+      </c>
+      <c r="C220" t="s">
+        <v>17</v>
+      </c>
+      <c r="D220" t="s">
+        <v>20</v>
+      </c>
+      <c r="F220" t="s">
+        <v>195</v>
+      </c>
+      <c r="G220" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7">
+      <c r="A221">
+        <v>6904</v>
+      </c>
+      <c r="B221" t="s">
+        <v>10</v>
+      </c>
+      <c r="C221" t="s">
+        <v>18</v>
+      </c>
+      <c r="D221" t="s">
+        <v>24</v>
+      </c>
+      <c r="F221" t="s">
+        <v>196</v>
+      </c>
+      <c r="G221" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7">
+      <c r="A222">
+        <v>8520</v>
+      </c>
+      <c r="B222" t="s">
+        <v>10</v>
+      </c>
+      <c r="C222" t="s">
+        <v>15</v>
+      </c>
+      <c r="D222" t="s">
+        <v>22</v>
+      </c>
+      <c r="G222" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7">
+      <c r="A223">
+        <v>1004</v>
+      </c>
+      <c r="B223" t="s">
+        <v>11</v>
+      </c>
+      <c r="C223" t="s">
+        <v>18</v>
+      </c>
+      <c r="D223" t="s">
+        <v>27</v>
+      </c>
+      <c r="F223" t="s">
+        <v>197</v>
+      </c>
+      <c r="G223" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7">
+      <c r="A224">
+        <v>5219</v>
+      </c>
+      <c r="B224" t="s">
+        <v>9</v>
+      </c>
+      <c r="C224" t="s">
+        <v>15</v>
+      </c>
+      <c r="D224" t="s">
+        <v>21</v>
+      </c>
+      <c r="F224" t="s">
+        <v>198</v>
+      </c>
+      <c r="G224" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7">
+      <c r="A225">
+        <v>5578</v>
+      </c>
+      <c r="B225" t="s">
+        <v>9</v>
+      </c>
+      <c r="C225" t="s">
+        <v>18</v>
+      </c>
+      <c r="D225" t="s">
+        <v>21</v>
+      </c>
+      <c r="G225" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7">
+      <c r="A226">
+        <v>7244</v>
+      </c>
+      <c r="B226" t="s">
+        <v>7</v>
+      </c>
+      <c r="C226" t="s">
+        <v>18</v>
+      </c>
+      <c r="D226" t="s">
+        <v>28</v>
+      </c>
+      <c r="F226" t="s">
+        <v>199</v>
+      </c>
+      <c r="G226" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7">
+      <c r="A227">
+        <v>3125</v>
+      </c>
+      <c r="B227" t="s">
+        <v>8</v>
+      </c>
+      <c r="C227" t="s">
+        <v>18</v>
+      </c>
+      <c r="D227" t="s">
+        <v>23</v>
+      </c>
+      <c r="F227" t="s">
+        <v>200</v>
+      </c>
+      <c r="G227" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7">
+      <c r="A228">
+        <v>2377</v>
+      </c>
+      <c r="B228" t="s">
+        <v>8</v>
+      </c>
+      <c r="C228" t="s">
+        <v>15</v>
+      </c>
+      <c r="D228" t="s">
+        <v>19</v>
+      </c>
+      <c r="G228" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7">
+      <c r="A229">
+        <v>6263</v>
+      </c>
+      <c r="B229" t="s">
+        <v>13</v>
+      </c>
+      <c r="C229" t="s">
+        <v>16</v>
+      </c>
+      <c r="D229" t="s">
+        <v>23</v>
+      </c>
+      <c r="G229" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7">
+      <c r="A230">
+        <v>5121</v>
+      </c>
+      <c r="B230" t="s">
+        <v>10</v>
+      </c>
+      <c r="C230" t="s">
+        <v>15</v>
+      </c>
+      <c r="D230" t="s">
+        <v>28</v>
+      </c>
+      <c r="F230" t="s">
+        <v>201</v>
+      </c>
+      <c r="G230" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7">
+      <c r="A231">
+        <v>5301</v>
+      </c>
+      <c r="B231" t="s">
+        <v>7</v>
+      </c>
+      <c r="C231" t="s">
+        <v>18</v>
+      </c>
+      <c r="D231" t="s">
+        <v>29</v>
+      </c>
+      <c r="F231" t="s">
+        <v>202</v>
+      </c>
+      <c r="G231" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7">
+      <c r="A232">
+        <v>7552</v>
+      </c>
+      <c r="B232" t="s">
+        <v>13</v>
+      </c>
+      <c r="C232" t="s">
+        <v>17</v>
+      </c>
+      <c r="D232" t="s">
+        <v>19</v>
+      </c>
+      <c r="F232" t="s">
+        <v>203</v>
+      </c>
+      <c r="G232" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7">
+      <c r="A233">
+        <v>5507</v>
+      </c>
+      <c r="B233" t="s">
+        <v>12</v>
+      </c>
+      <c r="C233" t="s">
+        <v>15</v>
+      </c>
+      <c r="D233" t="s">
+        <v>28</v>
+      </c>
+      <c r="F233" t="s">
+        <v>204</v>
+      </c>
+      <c r="G233" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7">
+      <c r="A234">
+        <v>2931</v>
+      </c>
+      <c r="B234" t="s">
+        <v>8</v>
+      </c>
+      <c r="C234" t="s">
+        <v>15</v>
+      </c>
+      <c r="D234" t="s">
+        <v>30</v>
+      </c>
+      <c r="F234" t="s">
+        <v>205</v>
+      </c>
+      <c r="G234" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7">
+      <c r="A235">
+        <v>1302</v>
+      </c>
+      <c r="B235" t="s">
+        <v>9</v>
+      </c>
+      <c r="C235" t="s">
+        <v>18</v>
+      </c>
+      <c r="D235" t="s">
+        <v>26</v>
+      </c>
+      <c r="F235" t="s">
+        <v>206</v>
+      </c>
+      <c r="G235" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7">
+      <c r="A236">
+        <v>3338</v>
+      </c>
+      <c r="B236" t="s">
+        <v>10</v>
+      </c>
+      <c r="C236" t="s">
+        <v>16</v>
+      </c>
+      <c r="D236" t="s">
+        <v>28</v>
+      </c>
+      <c r="G236" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7">
+      <c r="A237">
+        <v>5125</v>
+      </c>
+      <c r="B237" t="s">
+        <v>14</v>
+      </c>
+      <c r="C237" t="s">
+        <v>18</v>
+      </c>
+      <c r="D237" t="s">
+        <v>19</v>
+      </c>
+      <c r="G237" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7">
+      <c r="A238">
+        <v>4340</v>
+      </c>
+      <c r="B238" t="s">
+        <v>8</v>
+      </c>
+      <c r="C238" t="s">
+        <v>17</v>
+      </c>
+      <c r="D238" t="s">
+        <v>29</v>
+      </c>
+      <c r="G238" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7">
+      <c r="A239">
+        <v>7455</v>
+      </c>
+      <c r="B239" t="s">
+        <v>14</v>
+      </c>
+      <c r="C239" t="s">
+        <v>17</v>
+      </c>
+      <c r="D239" t="s">
+        <v>27</v>
+      </c>
+      <c r="F239" t="s">
+        <v>207</v>
+      </c>
+      <c r="G239" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7">
+      <c r="A240">
+        <v>1162</v>
+      </c>
+      <c r="B240" t="s">
+        <v>9</v>
+      </c>
+      <c r="C240" t="s">
+        <v>18</v>
+      </c>
+      <c r="D240" t="s">
+        <v>21</v>
+      </c>
+      <c r="G240" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7">
+      <c r="A241">
+        <v>2731</v>
+      </c>
+      <c r="B241" t="s">
+        <v>13</v>
+      </c>
+      <c r="C241" t="s">
+        <v>17</v>
+      </c>
+      <c r="D241" t="s">
+        <v>20</v>
+      </c>
+      <c r="F241" t="s">
+        <v>208</v>
+      </c>
+      <c r="G241" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7">
+      <c r="A242">
+        <v>2960</v>
+      </c>
+      <c r="B242" t="s">
+        <v>11</v>
+      </c>
+      <c r="C242" t="s">
+        <v>16</v>
+      </c>
+      <c r="D242" t="s">
+        <v>20</v>
+      </c>
+      <c r="G242" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7">
+      <c r="A243">
+        <v>7506</v>
+      </c>
+      <c r="B243" t="s">
+        <v>11</v>
+      </c>
+      <c r="C243" t="s">
+        <v>17</v>
+      </c>
+      <c r="D243" t="s">
+        <v>26</v>
+      </c>
+      <c r="F243" t="s">
+        <v>209</v>
+      </c>
+      <c r="G243" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7">
+      <c r="A244">
+        <v>3682</v>
+      </c>
+      <c r="B244" t="s">
+        <v>7</v>
+      </c>
+      <c r="C244" t="s">
+        <v>17</v>
+      </c>
+      <c r="D244" t="s">
+        <v>25</v>
+      </c>
+      <c r="F244" t="s">
+        <v>210</v>
+      </c>
+      <c r="G244" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7">
+      <c r="A245">
+        <v>6883</v>
+      </c>
+      <c r="B245" t="s">
+        <v>12</v>
+      </c>
+      <c r="C245" t="s">
+        <v>18</v>
+      </c>
+      <c r="D245" t="s">
+        <v>22</v>
+      </c>
+      <c r="F245" t="s">
+        <v>211</v>
+      </c>
+      <c r="G245" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7">
+      <c r="A246">
+        <v>5258</v>
+      </c>
+      <c r="B246" t="s">
+        <v>12</v>
+      </c>
+      <c r="C246" t="s">
+        <v>16</v>
+      </c>
+      <c r="D246" t="s">
+        <v>22</v>
+      </c>
+      <c r="G246" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7">
+      <c r="A247">
+        <v>2918</v>
+      </c>
+      <c r="B247" t="s">
+        <v>7</v>
+      </c>
+      <c r="C247" t="s">
+        <v>18</v>
+      </c>
+      <c r="D247" t="s">
+        <v>24</v>
+      </c>
+      <c r="G247" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7">
+      <c r="A248">
+        <v>4189</v>
+      </c>
+      <c r="B248" t="s">
+        <v>11</v>
+      </c>
+      <c r="C248" t="s">
+        <v>15</v>
+      </c>
+      <c r="D248" t="s">
+        <v>26</v>
+      </c>
+      <c r="F248" t="s">
+        <v>212</v>
+      </c>
+      <c r="G248" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7">
+      <c r="A249">
+        <v>1627</v>
+      </c>
+      <c r="B249" t="s">
+        <v>10</v>
+      </c>
+      <c r="C249" t="s">
+        <v>15</v>
+      </c>
+      <c r="D249" t="s">
+        <v>24</v>
+      </c>
+      <c r="F249" t="s">
+        <v>213</v>
+      </c>
+      <c r="G249" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7">
+      <c r="A250">
+        <v>1831</v>
+      </c>
+      <c r="B250" t="s">
+        <v>9</v>
+      </c>
+      <c r="C250" t="s">
+        <v>15</v>
+      </c>
+      <c r="D250" t="s">
+        <v>28</v>
+      </c>
+      <c r="F250" t="s">
+        <v>214</v>
+      </c>
+      <c r="G250" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7">
+      <c r="A251">
+        <v>5879</v>
+      </c>
+      <c r="B251" t="s">
+        <v>11</v>
+      </c>
+      <c r="C251" t="s">
+        <v>18</v>
+      </c>
+      <c r="D251" t="s">
+        <v>30</v>
+      </c>
+      <c r="F251" t="s">
+        <v>215</v>
+      </c>
+      <c r="G251" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7">
+      <c r="A252">
+        <v>8712</v>
+      </c>
+      <c r="B252" t="s">
+        <v>14</v>
+      </c>
+      <c r="C252" t="s">
+        <v>18</v>
+      </c>
+      <c r="D252" t="s">
+        <v>19</v>
+      </c>
+      <c r="F252" t="s">
+        <v>216</v>
+      </c>
+      <c r="G252" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7">
+      <c r="A253">
+        <v>1456</v>
+      </c>
+      <c r="B253" t="s">
+        <v>8</v>
+      </c>
+      <c r="C253" t="s">
+        <v>16</v>
+      </c>
+      <c r="D253" t="s">
+        <v>24</v>
+      </c>
+      <c r="F253" t="s">
+        <v>217</v>
+      </c>
+      <c r="G253" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7">
+      <c r="A254">
+        <v>1587</v>
+      </c>
+      <c r="B254" t="s">
+        <v>14</v>
+      </c>
+      <c r="C254" t="s">
+        <v>18</v>
+      </c>
+      <c r="D254" t="s">
+        <v>20</v>
+      </c>
+      <c r="F254" t="s">
+        <v>218</v>
+      </c>
+      <c r="G254" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7">
+      <c r="A255">
+        <v>3871</v>
+      </c>
+      <c r="B255" t="s">
+        <v>14</v>
+      </c>
+      <c r="C255" t="s">
+        <v>16</v>
+      </c>
+      <c r="D255" t="s">
+        <v>22</v>
+      </c>
+      <c r="F255" t="s">
+        <v>219</v>
+      </c>
+      <c r="G255" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7">
+      <c r="A256">
+        <v>5200</v>
+      </c>
+      <c r="B256" t="s">
+        <v>14</v>
+      </c>
+      <c r="C256" t="s">
+        <v>15</v>
+      </c>
+      <c r="D256" t="s">
+        <v>28</v>
+      </c>
+      <c r="F256" t="s">
+        <v>220</v>
+      </c>
+      <c r="G256" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7">
+      <c r="A257">
+        <v>5771</v>
+      </c>
+      <c r="B257" t="s">
+        <v>11</v>
+      </c>
+      <c r="C257" t="s">
+        <v>17</v>
+      </c>
+      <c r="D257" t="s">
+        <v>28</v>
+      </c>
+      <c r="F257" t="s">
+        <v>221</v>
+      </c>
+      <c r="G257" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7">
+      <c r="A258">
+        <v>1486</v>
+      </c>
+      <c r="B258" t="s">
+        <v>13</v>
+      </c>
+      <c r="C258" t="s">
+        <v>16</v>
+      </c>
+      <c r="D258" t="s">
+        <v>22</v>
+      </c>
+      <c r="F258" t="s">
+        <v>222</v>
+      </c>
+      <c r="G258" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7">
+      <c r="A259">
+        <v>4857</v>
+      </c>
+      <c r="B259" t="s">
+        <v>13</v>
+      </c>
+      <c r="C259" t="s">
+        <v>18</v>
+      </c>
+      <c r="D259" t="s">
+        <v>24</v>
+      </c>
+      <c r="G259" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7">
+      <c r="A260">
+        <v>6342</v>
+      </c>
+      <c r="B260" t="s">
+        <v>9</v>
+      </c>
+      <c r="C260" t="s">
+        <v>16</v>
+      </c>
+      <c r="D260" t="s">
+        <v>19</v>
+      </c>
+      <c r="F260" t="s">
+        <v>223</v>
+      </c>
+      <c r="G260" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7">
+      <c r="A261">
+        <v>3944</v>
+      </c>
+      <c r="B261" t="s">
+        <v>12</v>
+      </c>
+      <c r="C261" t="s">
+        <v>16</v>
+      </c>
+      <c r="D261" t="s">
+        <v>22</v>
+      </c>
+      <c r="F261" t="s">
+        <v>224</v>
+      </c>
+      <c r="G261" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7">
+      <c r="A262">
+        <v>7828</v>
+      </c>
+      <c r="B262" t="s">
+        <v>10</v>
+      </c>
+      <c r="C262" t="s">
+        <v>15</v>
+      </c>
+      <c r="D262" t="s">
+        <v>29</v>
+      </c>
+      <c r="F262" t="s">
+        <v>225</v>
+      </c>
+      <c r="G262" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7">
+      <c r="A263">
+        <v>3941</v>
+      </c>
+      <c r="B263" t="s">
+        <v>9</v>
+      </c>
+      <c r="C263" t="s">
+        <v>15</v>
+      </c>
+      <c r="D263" t="s">
+        <v>28</v>
+      </c>
+      <c r="F263" t="s">
+        <v>226</v>
+      </c>
+      <c r="G263" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7">
+      <c r="A264">
+        <v>6505</v>
+      </c>
+      <c r="B264" t="s">
+        <v>12</v>
+      </c>
+      <c r="C264" t="s">
+        <v>15</v>
+      </c>
+      <c r="D264" t="s">
+        <v>30</v>
+      </c>
+      <c r="G264" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7">
+      <c r="A265">
+        <v>2732</v>
+      </c>
+      <c r="B265" t="s">
+        <v>14</v>
+      </c>
+      <c r="C265" t="s">
+        <v>17</v>
+      </c>
+      <c r="D265" t="s">
+        <v>29</v>
+      </c>
+      <c r="F265" t="s">
+        <v>227</v>
+      </c>
+      <c r="G265" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7">
+      <c r="A266">
+        <v>2608</v>
+      </c>
+      <c r="B266" t="s">
+        <v>7</v>
+      </c>
+      <c r="C266" t="s">
+        <v>17</v>
+      </c>
+      <c r="D266" t="s">
+        <v>22</v>
+      </c>
+      <c r="F266" t="s">
+        <v>228</v>
+      </c>
+      <c r="G266" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7">
+      <c r="A267">
+        <v>9050</v>
+      </c>
+      <c r="B267" t="s">
+        <v>13</v>
+      </c>
+      <c r="C267" t="s">
+        <v>18</v>
+      </c>
+      <c r="D267" t="s">
+        <v>26</v>
+      </c>
+      <c r="F267" t="s">
+        <v>229</v>
+      </c>
+      <c r="G267" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7">
+      <c r="A268">
+        <v>7375</v>
+      </c>
+      <c r="B268" t="s">
+        <v>7</v>
+      </c>
+      <c r="C268" t="s">
+        <v>16</v>
+      </c>
+      <c r="D268" t="s">
+        <v>27</v>
+      </c>
+      <c r="F268" t="s">
+        <v>230</v>
+      </c>
+      <c r="G268" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7">
+      <c r="A269">
+        <v>7817</v>
+      </c>
+      <c r="B269" t="s">
+        <v>11</v>
+      </c>
+      <c r="C269" t="s">
+        <v>15</v>
+      </c>
+      <c r="D269" t="s">
+        <v>19</v>
+      </c>
+      <c r="F269" t="s">
+        <v>231</v>
+      </c>
+      <c r="G269" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7">
+      <c r="A270">
+        <v>7692</v>
+      </c>
+      <c r="B270" t="s">
+        <v>10</v>
+      </c>
+      <c r="C270" t="s">
+        <v>18</v>
+      </c>
+      <c r="D270" t="s">
+        <v>24</v>
+      </c>
+      <c r="F270" t="s">
+        <v>232</v>
+      </c>
+      <c r="G270" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7">
+      <c r="A271">
+        <v>8233</v>
+      </c>
+      <c r="B271" t="s">
+        <v>10</v>
+      </c>
+      <c r="C271" t="s">
+        <v>15</v>
+      </c>
+      <c r="D271" t="s">
+        <v>19</v>
+      </c>
+      <c r="G271" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7">
+      <c r="A272">
+        <v>2005</v>
+      </c>
+      <c r="B272" t="s">
+        <v>13</v>
+      </c>
+      <c r="C272" t="s">
+        <v>15</v>
+      </c>
+      <c r="D272" t="s">
+        <v>29</v>
+      </c>
+      <c r="F272" t="s">
+        <v>233</v>
+      </c>
+      <c r="G272" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7">
+      <c r="A273">
+        <v>2984</v>
+      </c>
+      <c r="B273" t="s">
+        <v>10</v>
+      </c>
+      <c r="C273" t="s">
+        <v>18</v>
+      </c>
+      <c r="D273" t="s">
+        <v>21</v>
+      </c>
+      <c r="F273" t="s">
+        <v>234</v>
+      </c>
+      <c r="G273" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7">
+      <c r="A274">
+        <v>9754</v>
+      </c>
+      <c r="B274" t="s">
+        <v>11</v>
+      </c>
+      <c r="C274" t="s">
+        <v>18</v>
+      </c>
+      <c r="D274" t="s">
+        <v>20</v>
+      </c>
+      <c r="F274" t="s">
+        <v>235</v>
+      </c>
+      <c r="G274" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7">
+      <c r="A275">
+        <v>6876</v>
+      </c>
+      <c r="B275" t="s">
+        <v>11</v>
+      </c>
+      <c r="C275" t="s">
+        <v>18</v>
+      </c>
+      <c r="D275" t="s">
+        <v>29</v>
+      </c>
+      <c r="F275" t="s">
+        <v>236</v>
+      </c>
+      <c r="G275" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7">
+      <c r="A276">
+        <v>3510</v>
+      </c>
+      <c r="B276" t="s">
+        <v>12</v>
+      </c>
+      <c r="C276" t="s">
+        <v>15</v>
+      </c>
+      <c r="D276" t="s">
+        <v>20</v>
+      </c>
+      <c r="G276" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7">
+      <c r="A277">
+        <v>6409</v>
+      </c>
+      <c r="B277" t="s">
+        <v>9</v>
+      </c>
+      <c r="C277" t="s">
+        <v>18</v>
+      </c>
+      <c r="D277" t="s">
+        <v>26</v>
+      </c>
+      <c r="G277" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7">
+      <c r="A278">
+        <v>4394</v>
+      </c>
+      <c r="B278" t="s">
+        <v>9</v>
+      </c>
+      <c r="C278" t="s">
+        <v>18</v>
+      </c>
+      <c r="D278" t="s">
+        <v>25</v>
+      </c>
+      <c r="G278" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7">
+      <c r="A279">
+        <v>1732</v>
+      </c>
+      <c r="B279" t="s">
+        <v>14</v>
+      </c>
+      <c r="C279" t="s">
+        <v>17</v>
+      </c>
+      <c r="D279" t="s">
+        <v>27</v>
+      </c>
+      <c r="F279" t="s">
+        <v>237</v>
+      </c>
+      <c r="G279" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7">
+      <c r="A280">
+        <v>9840</v>
+      </c>
+      <c r="B280" t="s">
+        <v>7</v>
+      </c>
+      <c r="C280" t="s">
+        <v>17</v>
+      </c>
+      <c r="D280" t="s">
+        <v>25</v>
+      </c>
+      <c r="G280" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7">
+      <c r="A281">
+        <v>5192</v>
+      </c>
+      <c r="B281" t="s">
+        <v>7</v>
+      </c>
+      <c r="C281" t="s">
+        <v>16</v>
+      </c>
+      <c r="D281" t="s">
+        <v>19</v>
+      </c>
+      <c r="F281" t="s">
+        <v>238</v>
+      </c>
+      <c r="G281" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7">
+      <c r="A282">
+        <v>6291</v>
+      </c>
+      <c r="B282" t="s">
+        <v>13</v>
+      </c>
+      <c r="C282" t="s">
+        <v>16</v>
+      </c>
+      <c r="D282" t="s">
+        <v>28</v>
+      </c>
+      <c r="F282" t="s">
+        <v>239</v>
+      </c>
+      <c r="G282" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7">
+      <c r="A283">
+        <v>8495</v>
+      </c>
+      <c r="B283" t="s">
+        <v>10</v>
+      </c>
+      <c r="C283" t="s">
+        <v>16</v>
+      </c>
+      <c r="D283" t="s">
+        <v>22</v>
+      </c>
+      <c r="F283" t="s">
+        <v>240</v>
+      </c>
+      <c r="G283" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7">
+      <c r="A284">
+        <v>7662</v>
+      </c>
+      <c r="B284" t="s">
+        <v>10</v>
+      </c>
+      <c r="C284" t="s">
+        <v>15</v>
+      </c>
+      <c r="D284" t="s">
+        <v>20</v>
+      </c>
+      <c r="F284" t="s">
+        <v>241</v>
+      </c>
+      <c r="G284" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7">
+      <c r="A285">
+        <v>2530</v>
+      </c>
+      <c r="B285" t="s">
+        <v>13</v>
+      </c>
+      <c r="C285" t="s">
+        <v>18</v>
+      </c>
+      <c r="D285" t="s">
+        <v>20</v>
+      </c>
+      <c r="F285" t="s">
+        <v>242</v>
+      </c>
+      <c r="G285" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7">
+      <c r="A286">
+        <v>8163</v>
+      </c>
+      <c r="B286" t="s">
+        <v>10</v>
+      </c>
+      <c r="C286" t="s">
+        <v>18</v>
+      </c>
+      <c r="D286" t="s">
+        <v>29</v>
+      </c>
+      <c r="F286" t="s">
+        <v>243</v>
+      </c>
+      <c r="G286" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7">
+      <c r="A287">
+        <v>5328</v>
+      </c>
+      <c r="B287" t="s">
+        <v>12</v>
+      </c>
+      <c r="C287" t="s">
+        <v>18</v>
+      </c>
+      <c r="D287" t="s">
+        <v>21</v>
+      </c>
+      <c r="F287" t="s">
+        <v>244</v>
+      </c>
+      <c r="G287" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7">
+      <c r="A288">
+        <v>7157</v>
+      </c>
+      <c r="B288" t="s">
+        <v>14</v>
+      </c>
+      <c r="C288" t="s">
+        <v>15</v>
+      </c>
+      <c r="D288" t="s">
+        <v>22</v>
+      </c>
+      <c r="F288" t="s">
+        <v>245</v>
+      </c>
+      <c r="G288" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="289" spans="1:7">
+      <c r="A289">
+        <v>2062</v>
+      </c>
+      <c r="B289" t="s">
+        <v>13</v>
+      </c>
+      <c r="C289" t="s">
+        <v>15</v>
+      </c>
+      <c r="D289" t="s">
+        <v>30</v>
+      </c>
+      <c r="F289" t="s">
+        <v>246</v>
+      </c>
+      <c r="G289" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7">
+      <c r="A290">
+        <v>9004</v>
+      </c>
+      <c r="B290" t="s">
+        <v>8</v>
+      </c>
+      <c r="C290" t="s">
+        <v>18</v>
+      </c>
+      <c r="D290" t="s">
+        <v>28</v>
+      </c>
+      <c r="F290" t="s">
+        <v>247</v>
+      </c>
+      <c r="G290" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7">
+      <c r="A291">
+        <v>6710</v>
+      </c>
+      <c r="B291" t="s">
+        <v>11</v>
+      </c>
+      <c r="C291" t="s">
+        <v>17</v>
+      </c>
+      <c r="D291" t="s">
+        <v>23</v>
+      </c>
+      <c r="F291" t="s">
+        <v>248</v>
+      </c>
+      <c r="G291" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7">
+      <c r="A292">
+        <v>4546</v>
+      </c>
+      <c r="B292" t="s">
+        <v>9</v>
+      </c>
+      <c r="C292" t="s">
+        <v>15</v>
+      </c>
+      <c r="D292" t="s">
+        <v>27</v>
+      </c>
+      <c r="F292" t="s">
+        <v>249</v>
+      </c>
+      <c r="G292" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7">
+      <c r="A293">
+        <v>7833</v>
+      </c>
+      <c r="B293" t="s">
+        <v>13</v>
+      </c>
+      <c r="C293" t="s">
+        <v>16</v>
+      </c>
+      <c r="D293" t="s">
+        <v>23</v>
+      </c>
+      <c r="F293" t="s">
+        <v>250</v>
+      </c>
+      <c r="G293" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7">
+      <c r="A294">
+        <v>6716</v>
+      </c>
+      <c r="B294" t="s">
+        <v>10</v>
+      </c>
+      <c r="C294" t="s">
+        <v>17</v>
+      </c>
+      <c r="D294" t="s">
+        <v>19</v>
+      </c>
+      <c r="G294" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7">
+      <c r="A295">
+        <v>3575</v>
+      </c>
+      <c r="B295" t="s">
+        <v>14</v>
+      </c>
+      <c r="C295" t="s">
+        <v>16</v>
+      </c>
+      <c r="D295" t="s">
+        <v>25</v>
+      </c>
+      <c r="F295" t="s">
+        <v>251</v>
+      </c>
+      <c r="G295" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7">
+      <c r="A296">
+        <v>8594</v>
+      </c>
+      <c r="B296" t="s">
+        <v>10</v>
+      </c>
+      <c r="C296" t="s">
+        <v>15</v>
+      </c>
+      <c r="D296" t="s">
+        <v>19</v>
+      </c>
+      <c r="G296" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7">
+      <c r="A297">
+        <v>5494</v>
+      </c>
+      <c r="B297" t="s">
+        <v>11</v>
+      </c>
+      <c r="C297" t="s">
+        <v>17</v>
+      </c>
+      <c r="D297" t="s">
+        <v>20</v>
+      </c>
+      <c r="F297" t="s">
+        <v>252</v>
+      </c>
+      <c r="G297" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7">
+      <c r="A298">
+        <v>9151</v>
+      </c>
+      <c r="B298" t="s">
+        <v>14</v>
+      </c>
+      <c r="C298" t="s">
+        <v>16</v>
+      </c>
+      <c r="D298" t="s">
+        <v>25</v>
+      </c>
+      <c r="F298" t="s">
+        <v>253</v>
+      </c>
+      <c r="G298" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7">
+      <c r="A299">
+        <v>2958</v>
+      </c>
+      <c r="B299" t="s">
+        <v>10</v>
+      </c>
+      <c r="C299" t="s">
+        <v>18</v>
+      </c>
+      <c r="D299" t="s">
+        <v>28</v>
+      </c>
+      <c r="F299" t="s">
+        <v>254</v>
+      </c>
+      <c r="G299" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7">
+      <c r="A300">
+        <v>6281</v>
+      </c>
+      <c r="B300" t="s">
+        <v>13</v>
+      </c>
+      <c r="C300" t="s">
+        <v>15</v>
+      </c>
+      <c r="D300" t="s">
+        <v>19</v>
+      </c>
+      <c r="F300" t="s">
+        <v>255</v>
+      </c>
+      <c r="G300" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7">
+      <c r="A301">
+        <v>3978</v>
+      </c>
+      <c r="B301" t="s">
+        <v>14</v>
+      </c>
+      <c r="C301" t="s">
+        <v>16</v>
+      </c>
+      <c r="D301" t="s">
+        <v>19</v>
+      </c>
+      <c r="G301" t="s">
+        <v>555</v>
       </c>
     </row>
   </sheetData>
